--- a/accessibility-knowledge-emergence/results/analysis/AttentionBindingPythiaModels-ClaudeInExcel.xlsx
+++ b/accessibility-knowledge-emergence/results/analysis/AttentionBindingPythiaModels-ClaudeInExcel.xlsx
@@ -5,12 +5,12 @@
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trishasalas/Repos/Research/how-models-think/accessibility-knowledge-emergence/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trishasalas/Repos/Research/how-models-think/accessibility-knowledge-emergence/results/analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{97B161AA-090F-5C43-BEBE-08375D11B887}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10FCDC74-43D0-E549-B254-7ABE56F5CBA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19200" activeTab="6" xr2:uid="{81DF49B0-1BA3-D947-B774-10FF709E1CBE}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17180" xr2:uid="{81DF49B0-1BA3-D947-B774-10FF709E1CBE}"/>
   </bookViews>
   <sheets>
     <sheet name="Claude Log" sheetId="12" r:id="rId1"/>
@@ -25,12 +25,12 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="12" r:id="rId10"/>
-    <pivotCache cacheId="16" r:id="rId11"/>
-    <pivotCache cacheId="20" r:id="rId12"/>
-    <pivotCache cacheId="24" r:id="rId13"/>
-    <pivotCache cacheId="28" r:id="rId14"/>
-    <pivotCache cacheId="32" r:id="rId15"/>
+    <pivotCache cacheId="0" r:id="rId10"/>
+    <pivotCache cacheId="1" r:id="rId11"/>
+    <pivotCache cacheId="2" r:id="rId12"/>
+    <pivotCache cacheId="3" r:id="rId13"/>
+    <pivotCache cacheId="4" r:id="rId14"/>
+    <pivotCache cacheId="5" r:id="rId15"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -1814,13 +1814,12 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="154">
+  <cellXfs count="152">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1942,9 +1941,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="35" borderId="22" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="33" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2224,13 +2220,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -13321,7 +13317,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3CE240DB-707F-A54A-8BB4-AFADC1D15944}" name="PivotTable8" cacheId="32" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3CE240DB-707F-A54A-8BB4-AFADC1D15944}" name="PivotTable8" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="F1:G14" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="3">
     <pivotField axis="axisRow" showAll="0">
@@ -13407,7 +13403,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{76CDFF73-92B8-0740-A6B4-3B46EC9403F1}" name="PivotTable6" cacheId="24" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{76CDFF73-92B8-0740-A6B4-3B46EC9403F1}" name="PivotTable6" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="F1:G19" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="3">
     <pivotField axis="axisRow" showAll="0">
@@ -13513,7 +13509,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B7F7BE44-ADA8-6240-85A0-7C941AF89FC7}" name="PivotTable3" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B7F7BE44-ADA8-6240-85A0-7C941AF89FC7}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="G2:H12" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="3">
     <pivotField axis="axisRow" showAll="0">
@@ -13587,7 +13583,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BD7FD2AD-F1CF-1147-BA80-96CBA00E7D67}" name="PivotTable5" cacheId="20" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BD7FD2AD-F1CF-1147-BA80-96CBA00E7D67}" name="PivotTable5" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="F1:G27" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="3">
     <pivotField axis="axisRow" showAll="0">
@@ -13725,7 +13721,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D9133390-85E7-F641-B9F3-4F440186A8FE}" name="PivotTable7" cacheId="28" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D9133390-85E7-F641-B9F3-4F440186A8FE}" name="PivotTable7" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="F1:G28" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="3">
     <pivotField axis="axisRow" showAll="0">
@@ -13867,7 +13863,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{38A4A439-8169-7647-B62D-7D8F47A9A905}" name="PivotTable4" cacheId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{38A4A439-8169-7647-B62D-7D8F47A9A905}" name="PivotTable4" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="F1:G28" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="3">
     <pivotField axis="axisRow" showAll="0">
@@ -14431,282 +14427,282 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A1" s="145" t="s">
+      <c r="A1" s="143" t="s">
         <v>207</v>
       </c>
-      <c r="B1" s="143" t="s">
+      <c r="B1" s="141" t="s">
         <v>208</v>
       </c>
-      <c r="C1" s="144" t="s">
+      <c r="C1" s="142" t="s">
         <v>209</v>
       </c>
-      <c r="D1" s="144" t="s">
+      <c r="D1" s="142" t="s">
         <v>210</v>
       </c>
-      <c r="E1" s="144" t="s">
+      <c r="E1" s="142" t="s">
         <v>211</v>
       </c>
-      <c r="F1" s="148" t="s">
+      <c r="F1" s="146" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="68" x14ac:dyDescent="0.2">
-      <c r="A2" s="146">
+      <c r="A2" s="144">
         <v>1</v>
       </c>
-      <c r="B2" s="139">
+      <c r="B2" s="137">
         <v>46096</v>
       </c>
-      <c r="C2" s="140" t="s">
+      <c r="C2" s="138" t="s">
         <v>213</v>
       </c>
-      <c r="D2" s="140" t="s">
+      <c r="D2" s="138" t="s">
         <v>214</v>
       </c>
-      <c r="E2" s="140" t="s">
+      <c r="E2" s="138" t="s">
         <v>215</v>
       </c>
-      <c r="F2" s="149" t="s">
+      <c r="F2" s="147" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="85" x14ac:dyDescent="0.2">
-      <c r="A3" s="146">
+      <c r="A3" s="144">
         <v>2</v>
       </c>
-      <c r="B3" s="139">
+      <c r="B3" s="137">
         <v>46096</v>
       </c>
-      <c r="C3" s="140" t="s">
+      <c r="C3" s="138" t="s">
         <v>217</v>
       </c>
-      <c r="D3" s="140" t="s">
+      <c r="D3" s="138" t="s">
         <v>218</v>
       </c>
-      <c r="E3" s="140" t="s">
+      <c r="E3" s="138" t="s">
         <v>219</v>
       </c>
-      <c r="F3" s="149" t="s">
+      <c r="F3" s="147" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="136" x14ac:dyDescent="0.2">
-      <c r="A4" s="146">
+      <c r="A4" s="144">
         <v>3</v>
       </c>
-      <c r="B4" s="139">
+      <c r="B4" s="137">
         <v>46096</v>
       </c>
-      <c r="C4" s="140" t="s">
+      <c r="C4" s="138" t="s">
         <v>221</v>
       </c>
-      <c r="D4" s="140" t="s">
+      <c r="D4" s="138" t="s">
         <v>222</v>
       </c>
-      <c r="E4" s="140" t="s">
+      <c r="E4" s="138" t="s">
         <v>223</v>
       </c>
-      <c r="F4" s="149" t="s">
+      <c r="F4" s="147" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="68" x14ac:dyDescent="0.2">
-      <c r="A5" s="146">
+      <c r="A5" s="144">
         <v>4</v>
       </c>
-      <c r="B5" s="139">
+      <c r="B5" s="137">
         <v>46096</v>
       </c>
-      <c r="C5" s="140" t="s">
+      <c r="C5" s="138" t="s">
         <v>225</v>
       </c>
-      <c r="D5" s="140" t="s">
+      <c r="D5" s="138" t="s">
         <v>226</v>
       </c>
-      <c r="E5" s="140" t="s">
+      <c r="E5" s="138" t="s">
         <v>227</v>
       </c>
-      <c r="F5" s="149" t="s">
+      <c r="F5" s="147" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="68" x14ac:dyDescent="0.2">
-      <c r="A6" s="146">
+      <c r="A6" s="144">
         <v>5</v>
       </c>
-      <c r="B6" s="139">
+      <c r="B6" s="137">
         <v>46096</v>
       </c>
-      <c r="C6" s="140" t="s">
+      <c r="C6" s="138" t="s">
         <v>229</v>
       </c>
-      <c r="D6" s="140" t="s">
+      <c r="D6" s="138" t="s">
         <v>230</v>
       </c>
-      <c r="E6" s="140" t="s">
+      <c r="E6" s="138" t="s">
         <v>231</v>
       </c>
-      <c r="F6" s="149" t="s">
+      <c r="F6" s="147" t="s">
         <v>232</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="85" x14ac:dyDescent="0.2">
-      <c r="A7" s="146">
+      <c r="A7" s="144">
         <v>6</v>
       </c>
-      <c r="B7" s="139">
+      <c r="B7" s="137">
         <v>46096</v>
       </c>
-      <c r="C7" s="140" t="s">
+      <c r="C7" s="138" t="s">
         <v>233</v>
       </c>
-      <c r="D7" s="140" t="s">
+      <c r="D7" s="138" t="s">
         <v>234</v>
       </c>
-      <c r="E7" s="140" t="s">
+      <c r="E7" s="138" t="s">
         <v>235</v>
       </c>
-      <c r="F7" s="149" t="s">
+      <c r="F7" s="147" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="136" x14ac:dyDescent="0.2">
-      <c r="A8" s="146">
+      <c r="A8" s="144">
         <v>7</v>
       </c>
-      <c r="B8" s="139">
+      <c r="B8" s="137">
         <v>46096</v>
       </c>
-      <c r="C8" s="140" t="s">
+      <c r="C8" s="138" t="s">
         <v>236</v>
       </c>
-      <c r="D8" s="140" t="s">
+      <c r="D8" s="138" t="s">
         <v>237</v>
       </c>
-      <c r="E8" s="140" t="s">
+      <c r="E8" s="138" t="s">
         <v>238</v>
       </c>
-      <c r="F8" s="149" t="s">
+      <c r="F8" s="147" t="s">
         <v>239</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="119" x14ac:dyDescent="0.2">
-      <c r="A9" s="146">
+      <c r="A9" s="144">
         <v>8</v>
       </c>
-      <c r="B9" s="139">
+      <c r="B9" s="137">
         <v>46096</v>
       </c>
-      <c r="C9" s="140" t="s">
+      <c r="C9" s="138" t="s">
         <v>240</v>
       </c>
-      <c r="D9" s="140" t="s">
+      <c r="D9" s="138" t="s">
         <v>241</v>
       </c>
-      <c r="E9" s="140" t="s">
+      <c r="E9" s="138" t="s">
         <v>242</v>
       </c>
-      <c r="F9" s="149" t="s">
+      <c r="F9" s="147" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="102" x14ac:dyDescent="0.2">
-      <c r="A10" s="146">
+      <c r="A10" s="144">
         <v>9</v>
       </c>
-      <c r="B10" s="139">
+      <c r="B10" s="137">
         <v>46096</v>
       </c>
-      <c r="C10" s="140" t="s">
+      <c r="C10" s="138" t="s">
         <v>244</v>
       </c>
-      <c r="D10" s="140" t="s">
+      <c r="D10" s="138" t="s">
         <v>245</v>
       </c>
-      <c r="E10" s="140" t="s">
+      <c r="E10" s="138" t="s">
         <v>246</v>
       </c>
-      <c r="F10" s="149" t="s">
+      <c r="F10" s="147" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="102" x14ac:dyDescent="0.2">
-      <c r="A11" s="146">
+      <c r="A11" s="144">
         <v>10</v>
       </c>
-      <c r="B11" s="139">
+      <c r="B11" s="137">
         <v>46096</v>
       </c>
-      <c r="C11" s="140" t="s">
+      <c r="C11" s="138" t="s">
         <v>248</v>
       </c>
-      <c r="D11" s="140" t="s">
+      <c r="D11" s="138" t="s">
         <v>249</v>
       </c>
-      <c r="E11" s="140" t="s">
+      <c r="E11" s="138" t="s">
         <v>250</v>
       </c>
-      <c r="F11" s="149" t="s">
+      <c r="F11" s="147" t="s">
         <v>251</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="68" x14ac:dyDescent="0.2">
-      <c r="A12" s="146">
+      <c r="A12" s="144">
         <v>11</v>
       </c>
-      <c r="B12" s="139">
+      <c r="B12" s="137">
         <v>46096</v>
       </c>
-      <c r="C12" s="140" t="s">
+      <c r="C12" s="138" t="s">
         <v>252</v>
       </c>
-      <c r="D12" s="140" t="s">
+      <c r="D12" s="138" t="s">
         <v>253</v>
       </c>
-      <c r="E12" s="140" t="s">
+      <c r="E12" s="138" t="s">
         <v>254</v>
       </c>
-      <c r="F12" s="149" t="s">
+      <c r="F12" s="147" t="s">
         <v>255</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="119" x14ac:dyDescent="0.2">
-      <c r="A13" s="147">
+      <c r="A13" s="145">
         <v>12</v>
       </c>
-      <c r="B13" s="141">
+      <c r="B13" s="139">
         <v>46096</v>
       </c>
-      <c r="C13" s="142" t="s">
+      <c r="C13" s="140" t="s">
         <v>256</v>
       </c>
-      <c r="D13" s="142" t="s">
+      <c r="D13" s="140" t="s">
         <v>257</v>
       </c>
-      <c r="E13" s="142" t="s">
+      <c r="E13" s="140" t="s">
         <v>258</v>
       </c>
-      <c r="F13" s="150" t="s">
+      <c r="F13" s="148" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="85" x14ac:dyDescent="0.2">
-      <c r="A14" s="151">
+      <c r="A14" s="149">
         <v>13</v>
       </c>
-      <c r="B14" s="138">
+      <c r="B14" s="136">
         <v>46096</v>
       </c>
-      <c r="C14" s="152" t="s">
+      <c r="C14" s="150" t="s">
         <v>260</v>
       </c>
-      <c r="D14" s="152" t="s">
+      <c r="D14" s="150" t="s">
         <v>261</v>
       </c>
-      <c r="E14" s="152" t="s">
+      <c r="E14" s="150" t="s">
         <v>262</v>
       </c>
-      <c r="F14" s="153" t="s">
+      <c r="F14" s="151" t="s">
         <v>263</v>
       </c>
     </row>
@@ -14755,7 +14751,7 @@
       <c r="F2" s="2">
         <v>0</v>
       </c>
-      <c r="G2" s="3">
+      <c r="G2">
         <v>29</v>
       </c>
     </row>
@@ -14772,7 +14768,7 @@
       <c r="F3" s="2">
         <v>1</v>
       </c>
-      <c r="G3" s="3">
+      <c r="G3">
         <v>29</v>
       </c>
     </row>
@@ -14789,7 +14785,7 @@
       <c r="F4" s="2">
         <v>2</v>
       </c>
-      <c r="G4" s="3">
+      <c r="G4">
         <v>56</v>
       </c>
     </row>
@@ -14806,7 +14802,7 @@
       <c r="F5" s="2">
         <v>3</v>
       </c>
-      <c r="G5" s="3">
+      <c r="G5">
         <v>32</v>
       </c>
     </row>
@@ -14823,7 +14819,7 @@
       <c r="F6" s="2">
         <v>4</v>
       </c>
-      <c r="G6" s="3">
+      <c r="G6">
         <v>11</v>
       </c>
     </row>
@@ -14840,7 +14836,7 @@
       <c r="F7" s="2">
         <v>5</v>
       </c>
-      <c r="G7" s="3">
+      <c r="G7">
         <v>20</v>
       </c>
     </row>
@@ -14857,7 +14853,7 @@
       <c r="F8" s="2">
         <v>6</v>
       </c>
-      <c r="G8" s="3">
+      <c r="G8">
         <v>14</v>
       </c>
     </row>
@@ -14874,7 +14870,7 @@
       <c r="F9" s="2">
         <v>7</v>
       </c>
-      <c r="G9" s="3">
+      <c r="G9">
         <v>15</v>
       </c>
     </row>
@@ -14891,7 +14887,7 @@
       <c r="F10" s="2">
         <v>8</v>
       </c>
-      <c r="G10" s="3">
+      <c r="G10">
         <v>10</v>
       </c>
     </row>
@@ -14908,7 +14904,7 @@
       <c r="F11" s="2">
         <v>9</v>
       </c>
-      <c r="G11" s="3">
+      <c r="G11">
         <v>3</v>
       </c>
     </row>
@@ -14925,7 +14921,7 @@
       <c r="F12" s="2">
         <v>10</v>
       </c>
-      <c r="G12" s="3">
+      <c r="G12">
         <v>9</v>
       </c>
     </row>
@@ -14942,7 +14938,7 @@
       <c r="F13" s="2">
         <v>11</v>
       </c>
-      <c r="G13" s="3">
+      <c r="G13">
         <v>14</v>
       </c>
     </row>
@@ -14959,7 +14955,7 @@
       <c r="F14" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14">
         <v>242</v>
       </c>
     </row>
@@ -15374,7 +15370,7 @@
       <c r="F2" s="2">
         <v>0</v>
       </c>
-      <c r="G2" s="3">
+      <c r="G2">
         <v>33</v>
       </c>
     </row>
@@ -15391,7 +15387,7 @@
       <c r="F3" s="2">
         <v>1</v>
       </c>
-      <c r="G3" s="3">
+      <c r="G3">
         <v>79</v>
       </c>
     </row>
@@ -15408,7 +15404,7 @@
       <c r="F4" s="2">
         <v>2</v>
       </c>
-      <c r="G4" s="3">
+      <c r="G4">
         <v>56</v>
       </c>
     </row>
@@ -15425,7 +15421,7 @@
       <c r="F5" s="2">
         <v>3</v>
       </c>
-      <c r="G5" s="3">
+      <c r="G5">
         <v>69</v>
       </c>
     </row>
@@ -15442,7 +15438,7 @@
       <c r="F6" s="2">
         <v>4</v>
       </c>
-      <c r="G6" s="3">
+      <c r="G6">
         <v>69</v>
       </c>
     </row>
@@ -15459,7 +15455,7 @@
       <c r="F7" s="2">
         <v>5</v>
       </c>
-      <c r="G7" s="3">
+      <c r="G7">
         <v>65</v>
       </c>
     </row>
@@ -15476,7 +15472,7 @@
       <c r="F8" s="2">
         <v>6</v>
       </c>
-      <c r="G8" s="3">
+      <c r="G8">
         <v>23</v>
       </c>
     </row>
@@ -15493,7 +15489,7 @@
       <c r="F9" s="2">
         <v>8</v>
       </c>
-      <c r="G9" s="3">
+      <c r="G9">
         <v>22</v>
       </c>
     </row>
@@ -15510,7 +15506,7 @@
       <c r="F10" s="2">
         <v>9</v>
       </c>
-      <c r="G10" s="3">
+      <c r="G10">
         <v>25</v>
       </c>
     </row>
@@ -15527,7 +15523,7 @@
       <c r="F11" s="2">
         <v>10</v>
       </c>
-      <c r="G11" s="3">
+      <c r="G11">
         <v>24</v>
       </c>
     </row>
@@ -15544,7 +15540,7 @@
       <c r="F12" s="2">
         <v>12</v>
       </c>
-      <c r="G12" s="3">
+      <c r="G12">
         <v>4</v>
       </c>
     </row>
@@ -15561,7 +15557,7 @@
       <c r="F13" s="2">
         <v>15</v>
       </c>
-      <c r="G13" s="3">
+      <c r="G13">
         <v>23</v>
       </c>
     </row>
@@ -15578,7 +15574,7 @@
       <c r="F14" s="2">
         <v>16</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14">
         <v>1</v>
       </c>
     </row>
@@ -15595,7 +15591,7 @@
       <c r="F15" s="2">
         <v>19</v>
       </c>
-      <c r="G15" s="3">
+      <c r="G15">
         <v>5</v>
       </c>
     </row>
@@ -15612,7 +15608,7 @@
       <c r="F16" s="2">
         <v>20</v>
       </c>
-      <c r="G16" s="3">
+      <c r="G16">
         <v>1</v>
       </c>
     </row>
@@ -15629,7 +15625,7 @@
       <c r="F17" s="2">
         <v>21</v>
       </c>
-      <c r="G17" s="3">
+      <c r="G17">
         <v>9</v>
       </c>
     </row>
@@ -15646,7 +15642,7 @@
       <c r="F18" s="2">
         <v>22</v>
       </c>
-      <c r="G18" s="3">
+      <c r="G18">
         <v>5</v>
       </c>
     </row>
@@ -15663,7 +15659,7 @@
       <c r="F19" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G19" s="3">
+      <c r="G19">
         <v>513</v>
       </c>
     </row>
@@ -16309,7 +16305,7 @@
       <c r="G3" s="2">
         <v>0</v>
       </c>
-      <c r="H3" s="3">
+      <c r="H3">
         <v>16</v>
       </c>
     </row>
@@ -16326,7 +16322,7 @@
       <c r="G4" s="2">
         <v>1</v>
       </c>
-      <c r="H4" s="3">
+      <c r="H4">
         <v>20</v>
       </c>
     </row>
@@ -16343,7 +16339,7 @@
       <c r="G5" s="2">
         <v>2</v>
       </c>
-      <c r="H5" s="3">
+      <c r="H5">
         <v>28</v>
       </c>
     </row>
@@ -16360,7 +16356,7 @@
       <c r="G6" s="2">
         <v>3</v>
       </c>
-      <c r="H6" s="3">
+      <c r="H6">
         <v>21</v>
       </c>
     </row>
@@ -16377,7 +16373,7 @@
       <c r="G7" s="2">
         <v>5</v>
       </c>
-      <c r="H7" s="3">
+      <c r="H7">
         <v>3</v>
       </c>
     </row>
@@ -16394,7 +16390,7 @@
       <c r="G8" s="2">
         <v>6</v>
       </c>
-      <c r="H8" s="3">
+      <c r="H8">
         <v>3</v>
       </c>
     </row>
@@ -16411,7 +16407,7 @@
       <c r="G9" s="2">
         <v>7</v>
       </c>
-      <c r="H9" s="3">
+      <c r="H9">
         <v>6</v>
       </c>
     </row>
@@ -16428,7 +16424,7 @@
       <c r="G10" s="2">
         <v>8</v>
       </c>
-      <c r="H10" s="3">
+      <c r="H10">
         <v>1</v>
       </c>
     </row>
@@ -16445,7 +16441,7 @@
       <c r="G11" s="2">
         <v>15</v>
       </c>
-      <c r="H11" s="3">
+      <c r="H11">
         <v>5</v>
       </c>
     </row>
@@ -16462,7 +16458,7 @@
       <c r="G12" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="H12" s="3">
+      <c r="H12">
         <v>103</v>
       </c>
     </row>
@@ -16701,7 +16697,7 @@
       <c r="F2" s="2">
         <v>0</v>
       </c>
-      <c r="G2" s="3">
+      <c r="G2">
         <v>299</v>
       </c>
     </row>
@@ -16718,7 +16714,7 @@
       <c r="F3" s="2">
         <v>1</v>
       </c>
-      <c r="G3" s="3">
+      <c r="G3">
         <v>398</v>
       </c>
     </row>
@@ -16735,7 +16731,7 @@
       <c r="F4" s="2">
         <v>2</v>
       </c>
-      <c r="G4" s="3">
+      <c r="G4">
         <v>157</v>
       </c>
     </row>
@@ -16752,7 +16748,7 @@
       <c r="F5" s="2">
         <v>3</v>
       </c>
-      <c r="G5" s="3">
+      <c r="G5">
         <v>109</v>
       </c>
     </row>
@@ -16769,7 +16765,7 @@
       <c r="F6" s="2">
         <v>4</v>
       </c>
-      <c r="G6" s="3">
+      <c r="G6">
         <v>64</v>
       </c>
     </row>
@@ -16786,7 +16782,7 @@
       <c r="F7" s="2">
         <v>5</v>
       </c>
-      <c r="G7" s="3">
+      <c r="G7">
         <v>40</v>
       </c>
     </row>
@@ -16803,7 +16799,7 @@
       <c r="F8" s="2">
         <v>6</v>
       </c>
-      <c r="G8" s="3">
+      <c r="G8">
         <v>19</v>
       </c>
     </row>
@@ -16820,7 +16816,7 @@
       <c r="F9" s="2">
         <v>8</v>
       </c>
-      <c r="G9" s="3">
+      <c r="G9">
         <v>20</v>
       </c>
     </row>
@@ -16837,7 +16833,7 @@
       <c r="F10" s="2">
         <v>9</v>
       </c>
-      <c r="G10" s="3">
+      <c r="G10">
         <v>37</v>
       </c>
     </row>
@@ -16854,7 +16850,7 @@
       <c r="F11" s="2">
         <v>10</v>
       </c>
-      <c r="G11" s="3">
+      <c r="G11">
         <v>67</v>
       </c>
     </row>
@@ -16871,7 +16867,7 @@
       <c r="F12" s="2">
         <v>11</v>
       </c>
-      <c r="G12" s="3">
+      <c r="G12">
         <v>57</v>
       </c>
     </row>
@@ -16888,7 +16884,7 @@
       <c r="F13" s="2">
         <v>12</v>
       </c>
-      <c r="G13" s="3">
+      <c r="G13">
         <v>67</v>
       </c>
     </row>
@@ -16905,7 +16901,7 @@
       <c r="F14" s="2">
         <v>14</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14">
         <v>21</v>
       </c>
     </row>
@@ -16922,7 +16918,7 @@
       <c r="F15" s="2">
         <v>20</v>
       </c>
-      <c r="G15" s="3">
+      <c r="G15">
         <v>47</v>
       </c>
     </row>
@@ -16939,7 +16935,7 @@
       <c r="F16" s="2">
         <v>21</v>
       </c>
-      <c r="G16" s="3">
+      <c r="G16">
         <v>24</v>
       </c>
     </row>
@@ -16956,7 +16952,7 @@
       <c r="F17" s="2">
         <v>22</v>
       </c>
-      <c r="G17" s="3">
+      <c r="G17">
         <v>52</v>
       </c>
     </row>
@@ -16973,7 +16969,7 @@
       <c r="F18" s="2">
         <v>23</v>
       </c>
-      <c r="G18" s="3">
+      <c r="G18">
         <v>12</v>
       </c>
     </row>
@@ -16990,7 +16986,7 @@
       <c r="F19" s="2">
         <v>24</v>
       </c>
-      <c r="G19" s="3">
+      <c r="G19">
         <v>15</v>
       </c>
     </row>
@@ -17007,7 +17003,7 @@
       <c r="F20" s="2">
         <v>25</v>
       </c>
-      <c r="G20" s="3">
+      <c r="G20">
         <v>7</v>
       </c>
     </row>
@@ -17024,7 +17020,7 @@
       <c r="F21" s="2">
         <v>26</v>
       </c>
-      <c r="G21" s="3">
+      <c r="G21">
         <v>4</v>
       </c>
     </row>
@@ -17041,7 +17037,7 @@
       <c r="F22" s="2">
         <v>27</v>
       </c>
-      <c r="G22" s="3">
+      <c r="G22">
         <v>34</v>
       </c>
     </row>
@@ -17058,7 +17054,7 @@
       <c r="F23" s="2">
         <v>28</v>
       </c>
-      <c r="G23" s="3">
+      <c r="G23">
         <v>15</v>
       </c>
     </row>
@@ -17075,7 +17071,7 @@
       <c r="F24" s="2">
         <v>29</v>
       </c>
-      <c r="G24" s="3">
+      <c r="G24">
         <v>7</v>
       </c>
     </row>
@@ -17092,7 +17088,7 @@
       <c r="F25" s="2">
         <v>30</v>
       </c>
-      <c r="G25" s="3">
+      <c r="G25">
         <v>38</v>
       </c>
     </row>
@@ -17109,7 +17105,7 @@
       <c r="F26" s="2">
         <v>31</v>
       </c>
-      <c r="G26" s="3">
+      <c r="G26">
         <v>23</v>
       </c>
     </row>
@@ -17126,7 +17122,7 @@
       <c r="F27" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G27" s="3">
+      <c r="G27">
         <v>1633</v>
       </c>
     </row>
@@ -18003,7 +17999,7 @@
       <c r="F2" s="2">
         <v>0</v>
       </c>
-      <c r="G2" s="3">
+      <c r="G2">
         <v>268</v>
       </c>
     </row>
@@ -18020,7 +18016,7 @@
       <c r="F3" s="2">
         <v>1</v>
       </c>
-      <c r="G3" s="3">
+      <c r="G3">
         <v>374</v>
       </c>
     </row>
@@ -18037,7 +18033,7 @@
       <c r="F4" s="2">
         <v>2</v>
       </c>
-      <c r="G4" s="3">
+      <c r="G4">
         <v>315</v>
       </c>
     </row>
@@ -18054,7 +18050,7 @@
       <c r="F5" s="2">
         <v>3</v>
       </c>
-      <c r="G5" s="3">
+      <c r="G5">
         <v>220</v>
       </c>
     </row>
@@ -18071,7 +18067,7 @@
       <c r="F6" s="2">
         <v>4</v>
       </c>
-      <c r="G6" s="3">
+      <c r="G6">
         <v>123</v>
       </c>
     </row>
@@ -18088,7 +18084,7 @@
       <c r="F7" s="2">
         <v>5</v>
       </c>
-      <c r="G7" s="3">
+      <c r="G7">
         <v>53</v>
       </c>
     </row>
@@ -18105,7 +18101,7 @@
       <c r="F8" s="2">
         <v>6</v>
       </c>
-      <c r="G8" s="3">
+      <c r="G8">
         <v>67</v>
       </c>
     </row>
@@ -18122,7 +18118,7 @@
       <c r="F9" s="2">
         <v>7</v>
       </c>
-      <c r="G9" s="3">
+      <c r="G9">
         <v>28</v>
       </c>
     </row>
@@ -18139,7 +18135,7 @@
       <c r="F10" s="2">
         <v>8</v>
       </c>
-      <c r="G10" s="3">
+      <c r="G10">
         <v>6</v>
       </c>
     </row>
@@ -18156,7 +18152,7 @@
       <c r="F11" s="2">
         <v>9</v>
       </c>
-      <c r="G11" s="3">
+      <c r="G11">
         <v>3</v>
       </c>
     </row>
@@ -18173,7 +18169,7 @@
       <c r="F12" s="2">
         <v>10</v>
       </c>
-      <c r="G12" s="3">
+      <c r="G12">
         <v>38</v>
       </c>
     </row>
@@ -18190,7 +18186,7 @@
       <c r="F13" s="2">
         <v>11</v>
       </c>
-      <c r="G13" s="3">
+      <c r="G13">
         <v>51</v>
       </c>
     </row>
@@ -18207,7 +18203,7 @@
       <c r="F14" s="2">
         <v>13</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14">
         <v>14</v>
       </c>
     </row>
@@ -18224,7 +18220,7 @@
       <c r="F15" s="2">
         <v>15</v>
       </c>
-      <c r="G15" s="3">
+      <c r="G15">
         <v>0</v>
       </c>
     </row>
@@ -18241,7 +18237,7 @@
       <c r="F16" s="2">
         <v>16</v>
       </c>
-      <c r="G16" s="3">
+      <c r="G16">
         <v>24</v>
       </c>
     </row>
@@ -18258,7 +18254,7 @@
       <c r="F17" s="2">
         <v>18</v>
       </c>
-      <c r="G17" s="3">
+      <c r="G17">
         <v>12</v>
       </c>
     </row>
@@ -18275,7 +18271,7 @@
       <c r="F18" s="2">
         <v>19</v>
       </c>
-      <c r="G18" s="3">
+      <c r="G18">
         <v>0</v>
       </c>
     </row>
@@ -18292,7 +18288,7 @@
       <c r="F19" s="2">
         <v>20</v>
       </c>
-      <c r="G19" s="3">
+      <c r="G19">
         <v>14</v>
       </c>
     </row>
@@ -18309,7 +18305,7 @@
       <c r="F20" s="2">
         <v>21</v>
       </c>
-      <c r="G20" s="3">
+      <c r="G20">
         <v>23</v>
       </c>
     </row>
@@ -18326,7 +18322,7 @@
       <c r="F21" s="2">
         <v>22</v>
       </c>
-      <c r="G21" s="3">
+      <c r="G21">
         <v>35</v>
       </c>
     </row>
@@ -18343,7 +18339,7 @@
       <c r="F22" s="2">
         <v>23</v>
       </c>
-      <c r="G22" s="3">
+      <c r="G22">
         <v>0</v>
       </c>
     </row>
@@ -18360,7 +18356,7 @@
       <c r="F23" s="2">
         <v>25</v>
       </c>
-      <c r="G23" s="3">
+      <c r="G23">
         <v>20</v>
       </c>
     </row>
@@ -18377,7 +18373,7 @@
       <c r="F24" s="2">
         <v>27</v>
       </c>
-      <c r="G24" s="3">
+      <c r="G24">
         <v>29</v>
       </c>
     </row>
@@ -18394,7 +18390,7 @@
       <c r="F25" s="2">
         <v>28</v>
       </c>
-      <c r="G25" s="3">
+      <c r="G25">
         <v>62</v>
       </c>
     </row>
@@ -18411,7 +18407,7 @@
       <c r="F26" s="2">
         <v>29</v>
       </c>
-      <c r="G26" s="3">
+      <c r="G26">
         <v>37</v>
       </c>
     </row>
@@ -18428,7 +18424,7 @@
       <c r="F27" s="2">
         <v>30</v>
       </c>
-      <c r="G27" s="3">
+      <c r="G27">
         <v>65</v>
       </c>
     </row>
@@ -18445,7 +18441,7 @@
       <c r="F28" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G28" s="3">
+      <c r="G28">
         <v>1881</v>
       </c>
     </row>
@@ -19554,7 +19550,7 @@
       <c r="F2" s="2">
         <v>0</v>
       </c>
-      <c r="G2" s="3">
+      <c r="G2">
         <v>510</v>
       </c>
     </row>
@@ -19571,7 +19567,7 @@
       <c r="F3" s="2">
         <v>1</v>
       </c>
-      <c r="G3" s="3">
+      <c r="G3">
         <v>497</v>
       </c>
     </row>
@@ -19585,11 +19581,11 @@
       <c r="C4">
         <v>0.2432</v>
       </c>
-      <c r="D4" s="4"/>
+      <c r="D4" s="3"/>
       <c r="F4" s="2">
         <v>2</v>
       </c>
-      <c r="G4" s="3">
+      <c r="G4">
         <v>260</v>
       </c>
     </row>
@@ -19606,7 +19602,7 @@
       <c r="F5" s="2">
         <v>3</v>
       </c>
-      <c r="G5" s="3">
+      <c r="G5">
         <v>180</v>
       </c>
     </row>
@@ -19623,7 +19619,7 @@
       <c r="F6" s="2">
         <v>4</v>
       </c>
-      <c r="G6" s="3">
+      <c r="G6">
         <v>64</v>
       </c>
     </row>
@@ -19640,7 +19636,7 @@
       <c r="F7" s="2">
         <v>5</v>
       </c>
-      <c r="G7" s="3">
+      <c r="G7">
         <v>33</v>
       </c>
     </row>
@@ -19657,7 +19653,7 @@
       <c r="F8" s="2">
         <v>6</v>
       </c>
-      <c r="G8" s="3">
+      <c r="G8">
         <v>6</v>
       </c>
     </row>
@@ -19674,7 +19670,7 @@
       <c r="F9" s="2">
         <v>7</v>
       </c>
-      <c r="G9" s="3">
+      <c r="G9">
         <v>31</v>
       </c>
     </row>
@@ -19691,7 +19687,7 @@
       <c r="F10" s="2">
         <v>8</v>
       </c>
-      <c r="G10" s="3">
+      <c r="G10">
         <v>45</v>
       </c>
     </row>
@@ -19708,7 +19704,7 @@
       <c r="F11" s="2">
         <v>9</v>
       </c>
-      <c r="G11" s="3">
+      <c r="G11">
         <v>94</v>
       </c>
     </row>
@@ -19725,7 +19721,7 @@
       <c r="F12" s="2">
         <v>10</v>
       </c>
-      <c r="G12" s="3">
+      <c r="G12">
         <v>1</v>
       </c>
     </row>
@@ -19742,7 +19738,7 @@
       <c r="F13" s="2">
         <v>11</v>
       </c>
-      <c r="G13" s="3">
+      <c r="G13">
         <v>33</v>
       </c>
     </row>
@@ -19759,7 +19755,7 @@
       <c r="F14" s="2">
         <v>12</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14">
         <v>47</v>
       </c>
     </row>
@@ -19776,7 +19772,7 @@
       <c r="F15" s="2">
         <v>14</v>
       </c>
-      <c r="G15" s="3">
+      <c r="G15">
         <v>7</v>
       </c>
     </row>
@@ -19793,7 +19789,7 @@
       <c r="F16" s="2">
         <v>15</v>
       </c>
-      <c r="G16" s="3">
+      <c r="G16">
         <v>8</v>
       </c>
     </row>
@@ -19810,7 +19806,7 @@
       <c r="F17" s="2">
         <v>16</v>
       </c>
-      <c r="G17" s="3">
+      <c r="G17">
         <v>70</v>
       </c>
     </row>
@@ -19827,7 +19823,7 @@
       <c r="F18" s="2">
         <v>18</v>
       </c>
-      <c r="G18" s="3">
+      <c r="G18">
         <v>59</v>
       </c>
     </row>
@@ -19844,7 +19840,7 @@
       <c r="F19" s="2">
         <v>19</v>
       </c>
-      <c r="G19" s="3">
+      <c r="G19">
         <v>87</v>
       </c>
     </row>
@@ -19861,7 +19857,7 @@
       <c r="F20" s="2">
         <v>25</v>
       </c>
-      <c r="G20" s="3">
+      <c r="G20">
         <v>30</v>
       </c>
     </row>
@@ -19878,7 +19874,7 @@
       <c r="F21" s="2">
         <v>26</v>
       </c>
-      <c r="G21" s="3">
+      <c r="G21">
         <v>9</v>
       </c>
     </row>
@@ -19895,7 +19891,7 @@
       <c r="F22" s="2">
         <v>29</v>
       </c>
-      <c r="G22" s="3">
+      <c r="G22">
         <v>34</v>
       </c>
     </row>
@@ -19912,7 +19908,7 @@
       <c r="F23" s="2">
         <v>30</v>
       </c>
-      <c r="G23" s="3">
+      <c r="G23">
         <v>0</v>
       </c>
     </row>
@@ -19929,7 +19925,7 @@
       <c r="F24" s="2">
         <v>32</v>
       </c>
-      <c r="G24" s="3">
+      <c r="G24">
         <v>36</v>
       </c>
     </row>
@@ -19946,7 +19942,7 @@
       <c r="F25" s="2">
         <v>33</v>
       </c>
-      <c r="G25" s="3">
+      <c r="G25">
         <v>162</v>
       </c>
     </row>
@@ -19963,7 +19959,7 @@
       <c r="F26" s="2">
         <v>34</v>
       </c>
-      <c r="G26" s="3">
+      <c r="G26">
         <v>51</v>
       </c>
     </row>
@@ -19980,7 +19976,7 @@
       <c r="F27" s="2">
         <v>35</v>
       </c>
-      <c r="G27" s="3">
+      <c r="G27">
         <v>2</v>
       </c>
     </row>
@@ -19997,7 +19993,7 @@
       <c r="F28" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G28" s="3">
+      <c r="G28">
         <v>2356</v>
       </c>
     </row>
@@ -21031,2046 +21027,2046 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="19" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="5" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A4" s="24" t="s">
+      <c r="A4" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="21" t="s">
+      <c r="B4" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="21" t="s">
+      <c r="C4" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="21" t="s">
+      <c r="D4" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="21" t="s">
+      <c r="E4" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="21" t="s">
+      <c r="F4" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="G4" s="21" t="s">
+      <c r="G4" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="H4" s="21" t="s">
+      <c r="H4" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="I4" s="21" t="s">
+      <c r="I4" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="J4" s="29" t="s">
+      <c r="J4" s="28" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A5" s="25" t="s">
+      <c r="A5" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="10">
+      <c r="C5" s="9">
         <v>12</v>
       </c>
-      <c r="D5" s="10">
+      <c r="D5" s="9">
         <v>12</v>
       </c>
-      <c r="E5" s="10">
-        <f>C5*D5</f>
+      <c r="E5" s="9">
+        <f t="shared" ref="E5:E10" si="0">C5*D5</f>
         <v>144</v>
       </c>
-      <c r="F5" s="10">
+      <c r="F5" s="9">
         <v>46</v>
       </c>
-      <c r="G5" s="11">
-        <f>F5/E5</f>
+      <c r="G5" s="10">
+        <f t="shared" ref="G5:G10" si="1">F5/E5</f>
         <v>0.31944444444444442</v>
       </c>
-      <c r="H5" s="12">
+      <c r="H5" s="11">
         <v>0.35610000000000003</v>
       </c>
-      <c r="I5" s="12">
+      <c r="I5" s="11">
         <v>1</v>
       </c>
-      <c r="J5" s="30">
+      <c r="J5" s="29">
         <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A6" s="26" t="s">
+      <c r="A6" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="13">
+      <c r="C6" s="12">
         <v>24</v>
       </c>
-      <c r="D6" s="13">
+      <c r="D6" s="12">
         <v>16</v>
       </c>
-      <c r="E6" s="13">
-        <f>C6*D6</f>
+      <c r="E6" s="12">
+        <f t="shared" si="0"/>
         <v>384</v>
       </c>
-      <c r="F6" s="13">
+      <c r="F6" s="12">
         <v>71</v>
       </c>
-      <c r="G6" s="14">
-        <f>F6/E6</f>
+      <c r="G6" s="13">
+        <f t="shared" si="1"/>
         <v>0.18489583333333334</v>
       </c>
-      <c r="H6" s="15">
+      <c r="H6" s="14">
         <v>0.37419999999999998</v>
       </c>
-      <c r="I6" s="15">
+      <c r="I6" s="14">
         <v>0.9758</v>
       </c>
-      <c r="J6" s="31">
+      <c r="J6" s="30">
         <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A7" s="25" t="s">
+      <c r="A7" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="C7" s="10">
+      <c r="C7" s="9">
         <v>16</v>
       </c>
-      <c r="D7" s="10">
+      <c r="D7" s="9">
         <v>8</v>
       </c>
-      <c r="E7" s="10">
-        <f>C7*D7</f>
+      <c r="E7" s="9">
+        <f t="shared" si="0"/>
         <v>128</v>
       </c>
-      <c r="F7" s="10">
+      <c r="F7" s="9">
         <v>28</v>
       </c>
-      <c r="G7" s="11">
-        <f>F7/E7</f>
+      <c r="G7" s="10">
+        <f t="shared" si="1"/>
         <v>0.21875</v>
       </c>
-      <c r="H7" s="12">
+      <c r="H7" s="11">
         <v>0.44209999999999999</v>
       </c>
-      <c r="I7" s="12">
+      <c r="I7" s="11">
         <v>0.99319999999999997</v>
       </c>
-      <c r="J7" s="30">
+      <c r="J7" s="29">
         <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A8" s="26" t="s">
+      <c r="A8" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="13">
+      <c r="C8" s="12">
         <v>32</v>
       </c>
-      <c r="D8" s="13">
+      <c r="D8" s="12">
         <v>32</v>
       </c>
-      <c r="E8" s="13">
-        <f>C8*D8</f>
+      <c r="E8" s="12">
+        <f t="shared" si="0"/>
         <v>1024</v>
       </c>
-      <c r="F8" s="13">
+      <c r="F8" s="12">
         <v>101</v>
       </c>
-      <c r="G8" s="14">
-        <f>F8/E8</f>
+      <c r="G8" s="13">
+        <f t="shared" si="1"/>
         <v>9.86328125E-2</v>
       </c>
-      <c r="H8" s="15">
+      <c r="H8" s="14">
         <v>0.35880000000000001</v>
       </c>
-      <c r="I8" s="15">
+      <c r="I8" s="14">
         <v>0.9909</v>
       </c>
-      <c r="J8" s="31">
+      <c r="J8" s="30">
         <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A9" s="25" t="s">
+      <c r="A9" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="10" t="s">
+      <c r="B9" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="10">
+      <c r="C9" s="9">
         <v>32</v>
       </c>
-      <c r="D9" s="10">
+      <c r="D9" s="9">
         <v>32</v>
       </c>
-      <c r="E9" s="10">
-        <f>C9*D9</f>
+      <c r="E9" s="9">
+        <f t="shared" si="0"/>
         <v>1024</v>
       </c>
-      <c r="F9" s="10">
+      <c r="F9" s="9">
         <v>123</v>
       </c>
-      <c r="G9" s="11">
-        <f>F9/E9</f>
+      <c r="G9" s="10">
+        <f t="shared" si="1"/>
         <v>0.1201171875</v>
       </c>
-      <c r="H9" s="12">
+      <c r="H9" s="11">
         <v>0.38740000000000002</v>
       </c>
-      <c r="I9" s="12">
+      <c r="I9" s="11">
         <v>0.98599999999999999</v>
       </c>
-      <c r="J9" s="30">
+      <c r="J9" s="29">
         <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A10" s="27" t="s">
+      <c r="A10" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="B10" s="17" t="s">
+      <c r="B10" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="C10" s="17">
+      <c r="C10" s="16">
         <v>36</v>
       </c>
-      <c r="D10" s="17">
+      <c r="D10" s="16">
         <v>40</v>
       </c>
-      <c r="E10" s="17">
-        <f>C10*D10</f>
+      <c r="E10" s="16">
+        <f t="shared" si="0"/>
         <v>1440</v>
       </c>
-      <c r="F10" s="17">
+      <c r="F10" s="16">
         <v>119</v>
       </c>
-      <c r="G10" s="18">
-        <f>F10/E10</f>
+      <c r="G10" s="17">
+        <f t="shared" si="1"/>
         <v>8.2638888888888887E-2</v>
       </c>
-      <c r="H10" s="19">
+      <c r="H10" s="18">
         <v>0.3664</v>
       </c>
-      <c r="I10" s="19">
+      <c r="I10" s="18">
         <v>0.99050000000000005</v>
       </c>
-      <c r="J10" s="32">
+      <c r="J10" s="31">
         <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="5" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A13" s="24" t="s">
+      <c r="A13" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="21" t="s">
+      <c r="B13" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="C13" s="21" t="s">
+      <c r="C13" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="D13" s="21" t="s">
+      <c r="D13" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="E13" s="21" t="s">
+      <c r="E13" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="F13" s="21" t="s">
+      <c r="F13" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="G13" s="21" t="s">
+      <c r="G13" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="H13" s="29" t="s">
+      <c r="H13" s="28" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A14" s="25" t="s">
+      <c r="A14" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="B14" s="10" t="s">
+      <c r="B14" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="C14" s="10">
+      <c r="C14" s="9">
         <v>23</v>
       </c>
-      <c r="D14" s="11">
-        <f>C14/F5</f>
+      <c r="D14" s="10">
+        <f t="shared" ref="D14:D19" si="2">C14/F5</f>
         <v>0.5</v>
       </c>
-      <c r="E14" s="10" t="s">
+      <c r="E14" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="F14" s="10">
+      <c r="F14" s="9">
         <v>18</v>
       </c>
-      <c r="G14" s="10" t="s">
+      <c r="G14" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="H14" s="30">
+      <c r="H14" s="29">
         <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A15" s="26" t="s">
+      <c r="A15" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="B15" s="13" t="s">
+      <c r="B15" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="C15" s="13">
+      <c r="C15" s="12">
         <v>48</v>
       </c>
-      <c r="D15" s="14">
-        <f>C15/F6</f>
+      <c r="D15" s="13">
+        <f t="shared" si="2"/>
         <v>0.676056338028169</v>
       </c>
-      <c r="E15" s="13" t="s">
+      <c r="E15" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="F15" s="13">
+      <c r="F15" s="12">
         <v>15</v>
       </c>
-      <c r="G15" s="13" t="s">
+      <c r="G15" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="H15" s="31">
+      <c r="H15" s="30">
         <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A16" s="25" t="s">
+      <c r="A16" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="B16" s="10" t="s">
+      <c r="B16" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="C16" s="10">
+      <c r="C16" s="9">
         <v>23</v>
       </c>
-      <c r="D16" s="11">
-        <f>C16/F7</f>
+      <c r="D16" s="10">
+        <f t="shared" si="2"/>
         <v>0.8214285714285714</v>
       </c>
-      <c r="E16" s="10" t="s">
+      <c r="E16" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="F16" s="10">
+      <c r="F16" s="9">
         <v>4</v>
       </c>
-      <c r="G16" s="10" t="s">
+      <c r="G16" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="H16" s="30">
+      <c r="H16" s="29">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A17" s="26" t="s">
+      <c r="A17" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="B17" s="13" t="s">
+      <c r="B17" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="C17" s="13">
+      <c r="C17" s="12">
         <v>66</v>
       </c>
-      <c r="D17" s="14">
-        <f>C17/F8</f>
+      <c r="D17" s="13">
+        <f t="shared" si="2"/>
         <v>0.65346534653465349</v>
       </c>
-      <c r="E17" s="13" t="s">
+      <c r="E17" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="F17" s="13">
+      <c r="F17" s="12">
         <v>22</v>
       </c>
-      <c r="G17" s="13" t="s">
+      <c r="G17" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="H17" s="31">
+      <c r="H17" s="30">
         <v>13</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A18" s="25" t="s">
+      <c r="A18" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="10" t="s">
+      <c r="B18" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="C18" s="10">
+      <c r="C18" s="9">
         <v>91</v>
       </c>
-      <c r="D18" s="11">
-        <f>C18/F9</f>
+      <c r="D18" s="10">
+        <f t="shared" si="2"/>
         <v>0.73983739837398377</v>
       </c>
-      <c r="E18" s="10" t="s">
+      <c r="E18" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="F18" s="10">
+      <c r="F18" s="9">
         <v>19</v>
       </c>
-      <c r="G18" s="10" t="s">
+      <c r="G18" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="H18" s="30">
+      <c r="H18" s="29">
         <v>13</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A19" s="27" t="s">
+      <c r="A19" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="B19" s="17" t="s">
+      <c r="B19" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="C19" s="17">
+      <c r="C19" s="16">
         <v>82</v>
       </c>
-      <c r="D19" s="18">
-        <f>C19/F10</f>
+      <c r="D19" s="17">
+        <f t="shared" si="2"/>
         <v>0.68907563025210083</v>
       </c>
-      <c r="E19" s="17" t="s">
+      <c r="E19" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="F19" s="17">
+      <c r="F19" s="16">
         <v>22</v>
       </c>
-      <c r="G19" s="17" t="s">
+      <c r="G19" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="H19" s="32">
+      <c r="H19" s="31">
         <v>15</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A21" s="6" t="s">
+      <c r="A21" s="5" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A22" s="24" t="s">
+      <c r="A22" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="B22" s="21" t="s">
+      <c r="B22" s="20" t="s">
         <v>54</v>
       </c>
-      <c r="C22" s="21" t="s">
+      <c r="C22" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="D22" s="21" t="s">
+      <c r="D22" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="E22" s="21" t="s">
+      <c r="E22" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="F22" s="21" t="s">
+      <c r="F22" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="G22" s="29" t="s">
+      <c r="G22" s="28" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A23" s="25" t="s">
+      <c r="A23" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="B23" s="12">
+      <c r="B23" s="11">
         <v>0.34</v>
       </c>
-      <c r="C23" s="12">
+      <c r="C23" s="11">
         <v>0.435</v>
       </c>
-      <c r="D23" s="12">
+      <c r="D23" s="11">
         <v>0.246</v>
       </c>
-      <c r="E23" s="12">
+      <c r="E23" s="11">
         <v>0.17299999999999999</v>
       </c>
-      <c r="F23" s="12">
+      <c r="F23" s="11">
         <v>0.629</v>
       </c>
-      <c r="G23" s="34">
-        <f>H5</f>
+      <c r="G23" s="33">
+        <f t="shared" ref="G23:G28" si="3">H5</f>
         <v>0.35610000000000003</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A24" s="26" t="s">
+      <c r="A24" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="B24" s="15">
+      <c r="B24" s="14">
         <v>0.46600000000000003</v>
       </c>
-      <c r="C24" s="15">
+      <c r="C24" s="14">
         <v>0.32</v>
       </c>
-      <c r="D24" s="15">
+      <c r="D24" s="14">
         <v>0.184</v>
       </c>
-      <c r="E24" s="15">
+      <c r="E24" s="14">
         <v>0.159</v>
       </c>
-      <c r="F24" s="15">
+      <c r="F24" s="14">
         <v>0.21299999999999999</v>
       </c>
-      <c r="G24" s="35">
-        <f>H6</f>
+      <c r="G24" s="34">
+        <f t="shared" si="3"/>
         <v>0.37419999999999998</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A25" s="25" t="s">
+      <c r="A25" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="B25" s="12">
+      <c r="B25" s="11">
         <v>0.48599999999999999</v>
       </c>
-      <c r="C25" s="12">
+      <c r="C25" s="11">
         <v>0.40100000000000002</v>
       </c>
-      <c r="D25" s="12">
+      <c r="D25" s="11">
         <v>0.13900000000000001</v>
       </c>
-      <c r="E25" s="12"/>
-      <c r="F25" s="12">
+      <c r="E25" s="11"/>
+      <c r="F25" s="11">
         <v>0.123</v>
       </c>
-      <c r="G25" s="34">
-        <f>H7</f>
+      <c r="G25" s="33">
+        <f t="shared" si="3"/>
         <v>0.44209999999999999</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A26" s="26" t="s">
+      <c r="A26" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="B26" s="15">
+      <c r="B26" s="14">
         <v>0.42799999999999999</v>
       </c>
-      <c r="C26" s="15">
+      <c r="C26" s="14">
         <v>0.24299999999999999</v>
       </c>
-      <c r="D26" s="15">
+      <c r="D26" s="14">
         <v>0.14099999999999999</v>
       </c>
-      <c r="E26" s="15">
+      <c r="E26" s="14">
         <v>0.17699999999999999</v>
       </c>
-      <c r="F26" s="15">
+      <c r="F26" s="14">
         <v>0.28999999999999998</v>
       </c>
-      <c r="G26" s="35">
-        <f>H8</f>
+      <c r="G26" s="34">
+        <f t="shared" si="3"/>
         <v>0.35880000000000001</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A27" s="25" t="s">
+      <c r="A27" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="12">
+      <c r="B27" s="11">
         <v>0.43</v>
       </c>
-      <c r="C27" s="12">
+      <c r="C27" s="11">
         <v>0.30499999999999999</v>
       </c>
-      <c r="D27" s="12">
+      <c r="D27" s="11">
         <v>0.32200000000000001</v>
       </c>
-      <c r="E27" s="12">
+      <c r="E27" s="11">
         <v>0.16600000000000001</v>
       </c>
-      <c r="F27" s="12">
+      <c r="F27" s="11">
         <v>0.31</v>
       </c>
-      <c r="G27" s="34">
-        <f>H9</f>
+      <c r="G27" s="33">
+        <f t="shared" si="3"/>
         <v>0.38740000000000002</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A28" s="27" t="s">
+      <c r="A28" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="B28" s="19">
+      <c r="B28" s="18">
         <v>0.38500000000000001</v>
       </c>
-      <c r="C28" s="19">
+      <c r="C28" s="18">
         <v>0.32800000000000001</v>
       </c>
-      <c r="D28" s="19">
+      <c r="D28" s="18">
         <v>0.26800000000000002</v>
       </c>
-      <c r="E28" s="19">
+      <c r="E28" s="18">
         <v>0.16700000000000001</v>
       </c>
-      <c r="F28" s="19">
+      <c r="F28" s="18">
         <v>0.4</v>
       </c>
-      <c r="G28" s="36">
-        <f>H10</f>
+      <c r="G28" s="35">
+        <f t="shared" si="3"/>
         <v>0.3664</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A30" s="6" t="s">
+      <c r="A30" s="5" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A31" s="24" t="s">
+      <c r="A31" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="B31" s="21" t="s">
+      <c r="B31" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="C31" s="21" t="s">
+      <c r="C31" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="D31" s="21" t="s">
+      <c r="D31" s="20" t="s">
         <v>63</v>
       </c>
-      <c r="E31" s="29" t="s">
+      <c r="E31" s="28" t="s">
         <v>64</v>
       </c>
-      <c r="G31" s="51" t="s">
+      <c r="G31" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="H31" s="51" t="s">
+      <c r="H31" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="I31" s="51" t="s">
+      <c r="I31" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="J31" s="51" t="s">
+      <c r="J31" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="K31" s="51" t="s">
+      <c r="K31" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="L31" s="51" t="s">
+      <c r="L31" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="M31" s="51" t="s">
+      <c r="M31" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="N31" s="51" t="s">
+      <c r="N31" s="6" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A32" s="25" t="s">
+      <c r="A32" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="B32" s="37">
+      <c r="B32" s="36">
         <v>160</v>
       </c>
-      <c r="C32" s="11">
-        <f>G5</f>
+      <c r="C32" s="10">
+        <f t="shared" ref="C32:C37" si="4">G5</f>
         <v>0.31944444444444442</v>
       </c>
-      <c r="D32" s="11">
-        <f>J5/F5</f>
+      <c r="D32" s="10">
+        <f t="shared" ref="D32:D37" si="5">J5/F5</f>
         <v>8.6956521739130432E-2</v>
       </c>
-      <c r="E32" s="40">
-        <f>D14</f>
+      <c r="E32" s="39">
+        <f t="shared" ref="E32:E37" si="6">D14</f>
         <v>0.5</v>
       </c>
-      <c r="G32" s="9">
-        <f>E5</f>
+      <c r="G32" s="8">
+        <f t="shared" ref="G32:H37" si="7">E5</f>
         <v>144</v>
       </c>
-      <c r="H32" s="9">
-        <f>F5</f>
+      <c r="H32" s="8">
+        <f t="shared" si="7"/>
         <v>46</v>
       </c>
-      <c r="I32" s="9">
-        <f>G32-H32</f>
+      <c r="I32" s="8">
+        <f t="shared" ref="I32:I37" si="8">G32-H32</f>
         <v>98</v>
       </c>
-      <c r="J32" s="8">
-        <f>G5</f>
+      <c r="J32" s="7">
+        <f t="shared" ref="J32:J37" si="9">G5</f>
         <v>0.31944444444444442</v>
       </c>
-      <c r="K32" s="8">
-        <f>1-J32</f>
+      <c r="K32" s="7">
+        <f t="shared" ref="K32:K37" si="10">1-J32</f>
         <v>0.68055555555555558</v>
       </c>
-      <c r="L32" s="58" t="str">
-        <f>A32</f>
+      <c r="L32" s="56" t="str">
+        <f t="shared" ref="L32:L37" si="11">A32</f>
         <v>160M</v>
       </c>
-      <c r="M32" s="4">
-        <f>H32</f>
+      <c r="M32" s="3">
+        <f t="shared" ref="M32:N37" si="12">H32</f>
         <v>46</v>
       </c>
-      <c r="N32" s="4">
-        <f>I32</f>
+      <c r="N32" s="3">
+        <f t="shared" si="12"/>
         <v>98</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A33" s="26" t="s">
+      <c r="A33" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="B33" s="38">
+      <c r="B33" s="37">
         <v>410</v>
       </c>
-      <c r="C33" s="14">
-        <f>G6</f>
+      <c r="C33" s="13">
+        <f t="shared" si="4"/>
         <v>0.18489583333333334</v>
       </c>
-      <c r="D33" s="14">
-        <f>J6/F6</f>
+      <c r="D33" s="13">
+        <f t="shared" si="5"/>
         <v>4.2253521126760563E-2</v>
       </c>
-      <c r="E33" s="41">
-        <f>D15</f>
+      <c r="E33" s="40">
+        <f t="shared" si="6"/>
         <v>0.676056338028169</v>
       </c>
-      <c r="G33" s="9">
-        <f>E6</f>
+      <c r="G33" s="8">
+        <f t="shared" si="7"/>
         <v>384</v>
       </c>
-      <c r="H33" s="9">
-        <f>F6</f>
+      <c r="H33" s="8">
+        <f t="shared" si="7"/>
         <v>71</v>
       </c>
-      <c r="I33" s="9">
-        <f>G33-H33</f>
+      <c r="I33" s="8">
+        <f t="shared" si="8"/>
         <v>313</v>
       </c>
-      <c r="J33" s="8">
-        <f>G6</f>
+      <c r="J33" s="7">
+        <f t="shared" si="9"/>
         <v>0.18489583333333334</v>
       </c>
-      <c r="K33" s="8">
-        <f>1-J33</f>
+      <c r="K33" s="7">
+        <f t="shared" si="10"/>
         <v>0.81510416666666663</v>
       </c>
-      <c r="L33" s="58" t="str">
-        <f>A33</f>
+      <c r="L33" s="56" t="str">
+        <f t="shared" si="11"/>
         <v>410M</v>
       </c>
-      <c r="M33" s="4">
-        <f>H33</f>
+      <c r="M33" s="3">
+        <f t="shared" si="12"/>
         <v>71</v>
       </c>
-      <c r="N33" s="4">
-        <f>I33</f>
+      <c r="N33" s="3">
+        <f t="shared" si="12"/>
         <v>313</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A34" s="25" t="s">
+      <c r="A34" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="B34" s="37">
+      <c r="B34" s="36">
         <v>1000</v>
       </c>
-      <c r="C34" s="11">
-        <f>G7</f>
+      <c r="C34" s="10">
+        <f t="shared" si="4"/>
         <v>0.21875</v>
       </c>
-      <c r="D34" s="11">
-        <f>J7/F7</f>
+      <c r="D34" s="10">
+        <f t="shared" si="5"/>
         <v>0.10714285714285714</v>
       </c>
-      <c r="E34" s="40">
-        <f>D16</f>
+      <c r="E34" s="39">
+        <f t="shared" si="6"/>
         <v>0.8214285714285714</v>
       </c>
-      <c r="G34" s="9">
-        <f>E7</f>
+      <c r="G34" s="8">
+        <f t="shared" si="7"/>
         <v>128</v>
       </c>
-      <c r="H34" s="9">
-        <f>F7</f>
+      <c r="H34" s="8">
+        <f t="shared" si="7"/>
         <v>28</v>
       </c>
-      <c r="I34" s="9">
-        <f>G34-H34</f>
+      <c r="I34" s="8">
+        <f t="shared" si="8"/>
         <v>100</v>
       </c>
-      <c r="J34" s="8">
-        <f>G7</f>
+      <c r="J34" s="7">
+        <f t="shared" si="9"/>
         <v>0.21875</v>
       </c>
-      <c r="K34" s="8">
-        <f>1-J34</f>
+      <c r="K34" s="7">
+        <f t="shared" si="10"/>
         <v>0.78125</v>
       </c>
-      <c r="L34" s="58" t="str">
-        <f>A34</f>
+      <c r="L34" s="56" t="str">
+        <f t="shared" si="11"/>
         <v>1B</v>
       </c>
-      <c r="M34" s="4">
-        <f>H34</f>
+      <c r="M34" s="3">
+        <f t="shared" si="12"/>
         <v>28</v>
       </c>
-      <c r="N34" s="4">
-        <f>I34</f>
+      <c r="N34" s="3">
+        <f t="shared" si="12"/>
         <v>100</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A35" s="26" t="s">
+      <c r="A35" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="B35" s="38">
+      <c r="B35" s="37">
         <v>2800</v>
       </c>
-      <c r="C35" s="14">
-        <f>G8</f>
+      <c r="C35" s="13">
+        <f t="shared" si="4"/>
         <v>9.86328125E-2</v>
       </c>
-      <c r="D35" s="14">
-        <f>J8/F8</f>
+      <c r="D35" s="13">
+        <f t="shared" si="5"/>
         <v>8.9108910891089105E-2</v>
       </c>
-      <c r="E35" s="41">
-        <f>D17</f>
+      <c r="E35" s="40">
+        <f t="shared" si="6"/>
         <v>0.65346534653465349</v>
       </c>
-      <c r="G35" s="9">
-        <f>E8</f>
+      <c r="G35" s="8">
+        <f t="shared" si="7"/>
         <v>1024</v>
       </c>
-      <c r="H35" s="9">
-        <f>F8</f>
+      <c r="H35" s="8">
+        <f t="shared" si="7"/>
         <v>101</v>
       </c>
-      <c r="I35" s="9">
-        <f>G35-H35</f>
+      <c r="I35" s="8">
+        <f t="shared" si="8"/>
         <v>923</v>
       </c>
-      <c r="J35" s="8">
-        <f>G8</f>
+      <c r="J35" s="7">
+        <f t="shared" si="9"/>
         <v>9.86328125E-2</v>
       </c>
-      <c r="K35" s="8">
-        <f>1-J35</f>
+      <c r="K35" s="7">
+        <f t="shared" si="10"/>
         <v>0.9013671875</v>
       </c>
-      <c r="L35" s="58" t="str">
-        <f>A35</f>
+      <c r="L35" s="56" t="str">
+        <f t="shared" si="11"/>
         <v>2.8B</v>
       </c>
-      <c r="M35" s="4">
-        <f>H35</f>
+      <c r="M35" s="3">
+        <f t="shared" si="12"/>
         <v>101</v>
       </c>
-      <c r="N35" s="4">
-        <f>I35</f>
+      <c r="N35" s="3">
+        <f t="shared" si="12"/>
         <v>923</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A36" s="25" t="s">
+      <c r="A36" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="B36" s="37">
+      <c r="B36" s="36">
         <v>6900</v>
       </c>
-      <c r="C36" s="11">
-        <f>G9</f>
+      <c r="C36" s="10">
+        <f t="shared" si="4"/>
         <v>0.1201171875</v>
       </c>
-      <c r="D36" s="11">
-        <f>J9/F9</f>
+      <c r="D36" s="10">
+        <f t="shared" si="5"/>
         <v>6.5040650406504072E-2</v>
       </c>
-      <c r="E36" s="40">
-        <f>D18</f>
+      <c r="E36" s="39">
+        <f t="shared" si="6"/>
         <v>0.73983739837398377</v>
       </c>
-      <c r="G36" s="9">
-        <f>E9</f>
+      <c r="G36" s="8">
+        <f t="shared" si="7"/>
         <v>1024</v>
       </c>
-      <c r="H36" s="9">
-        <f>F9</f>
+      <c r="H36" s="8">
+        <f t="shared" si="7"/>
         <v>123</v>
       </c>
-      <c r="I36" s="9">
-        <f>G36-H36</f>
+      <c r="I36" s="8">
+        <f t="shared" si="8"/>
         <v>901</v>
       </c>
-      <c r="J36" s="8">
-        <f>G9</f>
+      <c r="J36" s="7">
+        <f t="shared" si="9"/>
         <v>0.1201171875</v>
       </c>
-      <c r="K36" s="8">
-        <f>1-J36</f>
+      <c r="K36" s="7">
+        <f t="shared" si="10"/>
         <v>0.8798828125</v>
       </c>
-      <c r="L36" s="58" t="str">
-        <f>A36</f>
+      <c r="L36" s="56" t="str">
+        <f t="shared" si="11"/>
         <v>6.9B</v>
       </c>
-      <c r="M36" s="4">
-        <f>H36</f>
+      <c r="M36" s="3">
+        <f t="shared" si="12"/>
         <v>123</v>
       </c>
-      <c r="N36" s="4">
-        <f>I36</f>
+      <c r="N36" s="3">
+        <f t="shared" si="12"/>
         <v>901</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A37" s="27" t="s">
+      <c r="A37" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="B37" s="39">
+      <c r="B37" s="38">
         <v>12000</v>
       </c>
-      <c r="C37" s="18">
-        <f>G10</f>
+      <c r="C37" s="17">
+        <f t="shared" si="4"/>
         <v>8.2638888888888887E-2</v>
       </c>
-      <c r="D37" s="18">
-        <f>J10/F10</f>
+      <c r="D37" s="17">
+        <f t="shared" si="5"/>
         <v>5.8823529411764705E-2</v>
       </c>
-      <c r="E37" s="42">
-        <f>D19</f>
+      <c r="E37" s="41">
+        <f t="shared" si="6"/>
         <v>0.68907563025210083</v>
       </c>
-      <c r="G37" s="9">
-        <f>E10</f>
+      <c r="G37" s="8">
+        <f t="shared" si="7"/>
         <v>1440</v>
       </c>
-      <c r="H37" s="9">
-        <f>F10</f>
+      <c r="H37" s="8">
+        <f t="shared" si="7"/>
         <v>119</v>
       </c>
-      <c r="I37" s="9">
-        <f>G37-H37</f>
+      <c r="I37" s="8">
+        <f t="shared" si="8"/>
         <v>1321</v>
       </c>
-      <c r="J37" s="8">
-        <f>G10</f>
+      <c r="J37" s="7">
+        <f t="shared" si="9"/>
         <v>8.2638888888888887E-2</v>
       </c>
-      <c r="K37" s="8">
-        <f>1-J37</f>
+      <c r="K37" s="7">
+        <f t="shared" si="10"/>
         <v>0.91736111111111107</v>
       </c>
-      <c r="L37" s="58" t="str">
-        <f>A37</f>
+      <c r="L37" s="56" t="str">
+        <f t="shared" si="11"/>
         <v>12B</v>
       </c>
-      <c r="M37" s="4">
-        <f>H37</f>
+      <c r="M37" s="3">
+        <f t="shared" si="12"/>
         <v>119</v>
       </c>
-      <c r="N37" s="4">
-        <f>I37</f>
+      <c r="N37" s="3">
+        <f t="shared" si="12"/>
         <v>1321</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A39" s="6" t="s">
+      <c r="A39" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="L39" s="7" t="s">
+      <c r="L39" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="M39" s="7" t="s">
+      <c r="M39" s="6" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A40" s="24" t="s">
+      <c r="A40" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="B40" s="21" t="s">
+      <c r="B40" s="20" t="s">
         <v>66</v>
       </c>
-      <c r="C40" s="21" t="s">
+      <c r="C40" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="D40" s="21" t="s">
+      <c r="D40" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="E40" s="21" t="s">
+      <c r="E40" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="F40" s="29" t="s">
+      <c r="F40" s="28" t="s">
         <v>70</v>
       </c>
       <c r="L40" t="str">
-        <f>A32</f>
+        <f t="shared" ref="L40:L45" si="13">A32</f>
         <v>160M</v>
       </c>
-      <c r="M40" s="57">
-        <f>J32</f>
+      <c r="M40" s="55">
+        <f t="shared" ref="M40:M45" si="14">J32</f>
         <v>0.31944444444444442</v>
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A41" s="25" t="s">
+      <c r="A41" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="B41" s="10">
+      <c r="B41" s="9">
         <v>3</v>
       </c>
-      <c r="C41" s="12">
+      <c r="C41" s="11">
         <v>0.80100000000000005</v>
       </c>
-      <c r="D41" s="10" t="s">
+      <c r="D41" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="E41" s="12">
+      <c r="E41" s="11">
         <v>1</v>
       </c>
-      <c r="F41" s="40">
-        <f>B41/F5</f>
+      <c r="F41" s="39">
+        <f t="shared" ref="F41:F46" si="15">B41/F5</f>
         <v>6.5217391304347824E-2</v>
       </c>
       <c r="L41" t="str">
-        <f>A33</f>
+        <f t="shared" si="13"/>
         <v>410M</v>
       </c>
-      <c r="M41" s="57">
-        <f>J33</f>
+      <c r="M41" s="55">
+        <f t="shared" si="14"/>
         <v>0.18489583333333334</v>
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A42" s="26" t="s">
+      <c r="A42" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="B42" s="13">
+      <c r="B42" s="12">
         <v>2</v>
       </c>
-      <c r="C42" s="15">
+      <c r="C42" s="14">
         <v>0.22700000000000001</v>
       </c>
-      <c r="D42" s="13" t="s">
+      <c r="D42" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="E42" s="15">
+      <c r="E42" s="14">
         <v>0.33200000000000002</v>
       </c>
-      <c r="F42" s="41">
-        <f>B42/F6</f>
+      <c r="F42" s="40">
+        <f t="shared" si="15"/>
         <v>2.8169014084507043E-2</v>
       </c>
       <c r="L42" t="str">
-        <f>A34</f>
+        <f t="shared" si="13"/>
         <v>1B</v>
       </c>
-      <c r="M42" s="57">
-        <f>J34</f>
+      <c r="M42" s="55">
+        <f t="shared" si="14"/>
         <v>0.21875</v>
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A43" s="25" t="s">
+      <c r="A43" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="B43" s="10">
+      <c r="B43" s="9">
         <v>1</v>
       </c>
-      <c r="C43" s="12">
+      <c r="C43" s="11">
         <v>0.123</v>
       </c>
-      <c r="D43" s="10" t="s">
+      <c r="D43" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="E43" s="12">
+      <c r="E43" s="11">
         <v>0.123</v>
       </c>
-      <c r="F43" s="40">
-        <f>B43/F7</f>
+      <c r="F43" s="39">
+        <f t="shared" si="15"/>
         <v>3.5714285714285712E-2</v>
       </c>
       <c r="L43" t="str">
-        <f>A35</f>
+        <f t="shared" si="13"/>
         <v>2.8B</v>
       </c>
-      <c r="M43" s="57">
-        <f>J35</f>
+      <c r="M43" s="55">
+        <f t="shared" si="14"/>
         <v>9.86328125E-2</v>
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A44" s="26" t="s">
+      <c r="A44" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="B44" s="13">
+      <c r="B44" s="12">
         <v>4</v>
       </c>
-      <c r="C44" s="15">
+      <c r="C44" s="14">
         <v>0.34</v>
       </c>
-      <c r="D44" s="13" t="s">
+      <c r="D44" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="E44" s="15">
+      <c r="E44" s="14">
         <v>0.90200000000000002</v>
       </c>
-      <c r="F44" s="41">
-        <f>B44/F8</f>
+      <c r="F44" s="40">
+        <f t="shared" si="15"/>
         <v>3.9603960396039604E-2</v>
       </c>
       <c r="L44" t="str">
-        <f>A36</f>
+        <f t="shared" si="13"/>
         <v>6.9B</v>
       </c>
-      <c r="M44" s="57">
-        <f>J36</f>
+      <c r="M44" s="55">
+        <f t="shared" si="14"/>
         <v>0.1201171875</v>
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A45" s="25" t="s">
+      <c r="A45" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="B45" s="10">
+      <c r="B45" s="9">
         <v>6</v>
       </c>
-      <c r="C45" s="12">
+      <c r="C45" s="11">
         <v>0.27400000000000002</v>
       </c>
-      <c r="D45" s="10" t="s">
+      <c r="D45" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="E45" s="12">
+      <c r="E45" s="11">
         <v>0.73299999999999998</v>
       </c>
-      <c r="F45" s="40">
-        <f>B45/F9</f>
+      <c r="F45" s="39">
+        <f t="shared" si="15"/>
         <v>4.878048780487805E-2</v>
       </c>
       <c r="L45" t="str">
-        <f>A37</f>
+        <f t="shared" si="13"/>
         <v>12B</v>
       </c>
-      <c r="M45" s="57">
-        <f>J37</f>
+      <c r="M45" s="55">
+        <f t="shared" si="14"/>
         <v>8.2638888888888887E-2</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A46" s="27" t="s">
+      <c r="A46" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="B46" s="17">
+      <c r="B46" s="16">
         <v>11</v>
       </c>
-      <c r="C46" s="19">
+      <c r="C46" s="18">
         <v>0.43099999999999999</v>
       </c>
-      <c r="D46" s="17" t="s">
+      <c r="D46" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="E46" s="19">
+      <c r="E46" s="18">
         <v>0.877</v>
       </c>
-      <c r="F46" s="42">
-        <f>B46/F10</f>
+      <c r="F46" s="41">
+        <f t="shared" si="15"/>
         <v>9.2436974789915971E-2</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A65" s="6" t="s">
+      <c r="A65" s="5" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A66" s="24" t="s">
+      <c r="A66" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="B66" s="21" t="s">
+      <c r="B66" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="C66" s="21" t="s">
+      <c r="C66" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="D66" s="29" t="s">
+      <c r="D66" s="28" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A67" s="26" t="s">
+      <c r="A67" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="B67" s="14">
-        <f>C14/F5</f>
+      <c r="B67" s="13">
+        <f t="shared" ref="B67:B72" si="16">C14/F5</f>
         <v>0.5</v>
       </c>
-      <c r="C67" s="14">
-        <f>F14/F5</f>
+      <c r="C67" s="13">
+        <f t="shared" ref="C67:C72" si="17">F14/F5</f>
         <v>0.39130434782608697</v>
       </c>
-      <c r="D67" s="41">
-        <f>H14/F5</f>
+      <c r="D67" s="40">
+        <f t="shared" ref="D67:D72" si="18">H14/F5</f>
         <v>0.10869565217391304</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A68" s="26" t="s">
+      <c r="A68" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="B68" s="14">
-        <f>C15/F6</f>
+      <c r="B68" s="13">
+        <f t="shared" si="16"/>
         <v>0.676056338028169</v>
       </c>
-      <c r="C68" s="14">
-        <f>F15/F6</f>
+      <c r="C68" s="13">
+        <f t="shared" si="17"/>
         <v>0.21126760563380281</v>
       </c>
-      <c r="D68" s="41">
-        <f>H15/F6</f>
+      <c r="D68" s="40">
+        <f t="shared" si="18"/>
         <v>0.11267605633802817</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A69" s="26" t="s">
+      <c r="A69" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="B69" s="14">
-        <f>C16/F7</f>
+      <c r="B69" s="13">
+        <f t="shared" si="16"/>
         <v>0.8214285714285714</v>
       </c>
-      <c r="C69" s="14">
-        <f>F16/F7</f>
+      <c r="C69" s="13">
+        <f t="shared" si="17"/>
         <v>0.14285714285714285</v>
       </c>
-      <c r="D69" s="41">
-        <f>H16/F7</f>
+      <c r="D69" s="40">
+        <f t="shared" si="18"/>
         <v>3.5714285714285712E-2</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A70" s="26" t="s">
+      <c r="A70" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="B70" s="14">
-        <f>C17/F8</f>
+      <c r="B70" s="13">
+        <f t="shared" si="16"/>
         <v>0.65346534653465349</v>
       </c>
-      <c r="C70" s="14">
-        <f>F17/F8</f>
+      <c r="C70" s="13">
+        <f t="shared" si="17"/>
         <v>0.21782178217821782</v>
       </c>
-      <c r="D70" s="41">
-        <f>H17/F8</f>
+      <c r="D70" s="40">
+        <f t="shared" si="18"/>
         <v>0.12871287128712872</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A71" s="26" t="s">
+      <c r="A71" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="B71" s="14">
-        <f>C18/F9</f>
+      <c r="B71" s="13">
+        <f t="shared" si="16"/>
         <v>0.73983739837398377</v>
       </c>
-      <c r="C71" s="14">
-        <f>F18/F9</f>
+      <c r="C71" s="13">
+        <f t="shared" si="17"/>
         <v>0.15447154471544716</v>
       </c>
-      <c r="D71" s="41">
-        <f>H18/F9</f>
+      <c r="D71" s="40">
+        <f t="shared" si="18"/>
         <v>0.10569105691056911</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A72" s="27" t="s">
+      <c r="A72" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="B72" s="18">
-        <f>C19/F10</f>
+      <c r="B72" s="17">
+        <f t="shared" si="16"/>
         <v>0.68907563025210083</v>
       </c>
-      <c r="C72" s="18">
-        <f>F19/F10</f>
+      <c r="C72" s="17">
+        <f t="shared" si="17"/>
         <v>0.18487394957983194</v>
       </c>
-      <c r="D72" s="42">
-        <f>H19/F10</f>
+      <c r="D72" s="41">
+        <f t="shared" si="18"/>
         <v>0.12605042016806722</v>
       </c>
     </row>
     <row r="93" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A93" s="6" t="s">
+      <c r="A93" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="G93" s="6" t="s">
+      <c r="G93" s="5" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="94" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A94" s="24" t="s">
+      <c r="A94" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="B94" s="21" t="s">
+      <c r="B94" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="C94" s="21" t="s">
+      <c r="C94" s="20" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="21" t="s">
+      <c r="D94" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="E94" s="29" t="s">
+      <c r="E94" s="28" t="s">
         <v>85</v>
       </c>
-      <c r="G94" s="52" t="s">
+      <c r="G94" s="50" t="s">
         <v>85</v>
       </c>
-      <c r="H94" s="20" t="s">
+      <c r="H94" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="I94" s="20" t="s">
+      <c r="I94" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="J94" s="20" t="s">
+      <c r="J94" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="K94" s="20" t="s">
+      <c r="K94" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="L94" s="20" t="s">
+      <c r="L94" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="M94" s="55" t="s">
+      <c r="M94" s="53" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="95" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A95" s="47" t="s">
+      <c r="A95" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="B95" s="43">
+      <c r="B95" s="42">
         <v>11</v>
       </c>
-      <c r="C95" s="43">
+      <c r="C95" s="42">
         <v>8</v>
       </c>
-      <c r="D95" s="44">
+      <c r="D95" s="43">
         <v>1</v>
       </c>
-      <c r="E95" s="49">
+      <c r="E95" s="48">
         <f>B95/(12-1)</f>
         <v>1</v>
       </c>
-      <c r="G95" s="53" t="s">
+      <c r="G95" s="51" t="s">
         <v>87</v>
       </c>
-      <c r="H95" s="15"/>
-      <c r="I95" s="15">
+      <c r="H95" s="14"/>
+      <c r="I95" s="14">
         <v>0.9758</v>
       </c>
-      <c r="J95" s="15">
+      <c r="J95" s="14">
         <v>0.96560000000000001</v>
       </c>
-      <c r="K95" s="15">
+      <c r="K95" s="14">
         <v>0.97260000000000002</v>
       </c>
-      <c r="L95" s="15"/>
-      <c r="M95" s="33"/>
+      <c r="L95" s="14"/>
+      <c r="M95" s="32"/>
     </row>
     <row r="96" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A96" s="47" t="s">
+      <c r="A96" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="B96" s="43">
+      <c r="B96" s="42">
         <v>11</v>
       </c>
-      <c r="C96" s="43">
+      <c r="C96" s="42">
         <v>6</v>
       </c>
-      <c r="D96" s="44">
+      <c r="D96" s="43">
         <v>0.97119999999999995</v>
       </c>
-      <c r="E96" s="49">
+      <c r="E96" s="48">
         <f>B96/(12-1)</f>
         <v>1</v>
       </c>
-      <c r="G96" s="53" t="s">
+      <c r="G96" s="51" t="s">
         <v>88</v>
       </c>
-      <c r="H96" s="15"/>
-      <c r="I96" s="15">
+      <c r="H96" s="14"/>
+      <c r="I96" s="14">
         <v>0.94040000000000001</v>
       </c>
-      <c r="J96" s="15">
+      <c r="J96" s="14">
         <v>0.97040000000000004</v>
       </c>
-      <c r="K96" s="15">
+      <c r="K96" s="14">
         <v>0.9909</v>
       </c>
-      <c r="L96" s="15">
+      <c r="L96" s="14">
         <v>0.96009999999999995</v>
       </c>
-      <c r="M96" s="33">
+      <c r="M96" s="32">
         <v>0.99050000000000005</v>
       </c>
     </row>
     <row r="97" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A97" s="47" t="s">
+      <c r="A97" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="B97" s="43">
+      <c r="B97" s="42">
         <v>3</v>
       </c>
-      <c r="C97" s="43">
+      <c r="C97" s="42">
         <v>0</v>
       </c>
-      <c r="D97" s="44">
+      <c r="D97" s="43">
         <v>0.92430000000000001</v>
       </c>
-      <c r="E97" s="49">
+      <c r="E97" s="48">
         <f>B97/(12-1)</f>
         <v>0.27272727272727271</v>
       </c>
-      <c r="G97" s="53" t="s">
+      <c r="G97" s="51" t="s">
         <v>89</v>
       </c>
-      <c r="H97" s="15"/>
-      <c r="I97" s="15">
+      <c r="H97" s="14"/>
+      <c r="I97" s="14">
         <v>0.95909999999999995</v>
       </c>
-      <c r="J97" s="15">
+      <c r="J97" s="14">
         <v>0.99319999999999997</v>
       </c>
-      <c r="K97" s="15"/>
-      <c r="L97" s="15">
+      <c r="K97" s="14"/>
+      <c r="L97" s="14">
         <v>0.98599999999999999</v>
       </c>
-      <c r="M97" s="33">
+      <c r="M97" s="32">
         <v>0.96750000000000003</v>
       </c>
     </row>
     <row r="98" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A98" s="47" t="s">
+      <c r="A98" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="B98" s="43">
+      <c r="B98" s="42">
         <v>3</v>
       </c>
-      <c r="C98" s="43">
+      <c r="C98" s="42">
         <v>2</v>
       </c>
-      <c r="D98" s="44">
+      <c r="D98" s="43">
         <v>0.91559999999999997</v>
       </c>
-      <c r="E98" s="49">
+      <c r="E98" s="48">
         <f>B98/(12-1)</f>
         <v>0.27272727272727271</v>
       </c>
-      <c r="G98" s="53" t="s">
+      <c r="G98" s="51" t="s">
         <v>90</v>
       </c>
-      <c r="H98" s="15"/>
-      <c r="I98" s="15"/>
-      <c r="J98" s="15"/>
-      <c r="K98" s="15"/>
-      <c r="L98" s="15"/>
-      <c r="M98" s="33"/>
+      <c r="H98" s="14"/>
+      <c r="I98" s="14"/>
+      <c r="J98" s="14"/>
+      <c r="K98" s="14"/>
+      <c r="L98" s="14"/>
+      <c r="M98" s="32"/>
     </row>
     <row r="99" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A99" s="47" t="s">
+      <c r="A99" s="46" t="s">
         <v>21</v>
       </c>
-      <c r="B99" s="43">
+      <c r="B99" s="42">
         <v>0</v>
       </c>
-      <c r="C99" s="43">
+      <c r="C99" s="42">
         <v>14</v>
       </c>
-      <c r="D99" s="44">
+      <c r="D99" s="43">
         <v>0.9758</v>
       </c>
-      <c r="E99" s="49">
+      <c r="E99" s="48">
         <f>B99/(24-1)</f>
         <v>0</v>
       </c>
-      <c r="G99" s="53" t="s">
+      <c r="G99" s="51" t="s">
         <v>91</v>
       </c>
-      <c r="H99" s="15">
+      <c r="H99" s="14">
         <v>0.92430000000000001</v>
       </c>
-      <c r="I99" s="15"/>
-      <c r="J99" s="15"/>
-      <c r="K99" s="15"/>
-      <c r="L99" s="15"/>
-      <c r="M99" s="33"/>
+      <c r="I99" s="14"/>
+      <c r="J99" s="14"/>
+      <c r="K99" s="14"/>
+      <c r="L99" s="14"/>
+      <c r="M99" s="32"/>
     </row>
     <row r="100" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A100" s="47" t="s">
+      <c r="A100" s="46" t="s">
         <v>21</v>
       </c>
-      <c r="B100" s="43">
+      <c r="B100" s="42">
         <v>3</v>
       </c>
-      <c r="C100" s="43">
+      <c r="C100" s="42">
         <v>13</v>
       </c>
-      <c r="D100" s="44">
+      <c r="D100" s="43">
         <v>0.95909999999999995</v>
       </c>
-      <c r="E100" s="49">
+      <c r="E100" s="48">
         <f>B100/(24-1)</f>
         <v>0.13043478260869565</v>
       </c>
-      <c r="G100" s="53" t="s">
+      <c r="G100" s="51" t="s">
         <v>92</v>
       </c>
-      <c r="H100" s="15"/>
-      <c r="I100" s="15"/>
-      <c r="J100" s="15"/>
-      <c r="K100" s="15">
+      <c r="H100" s="14"/>
+      <c r="I100" s="14"/>
+      <c r="J100" s="14"/>
+      <c r="K100" s="14">
         <v>0.90190000000000003</v>
       </c>
-      <c r="L100" s="15"/>
-      <c r="M100" s="33"/>
+      <c r="L100" s="14"/>
+      <c r="M100" s="32"/>
     </row>
     <row r="101" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A101" s="47" t="s">
+      <c r="A101" s="46" t="s">
         <v>21</v>
       </c>
-      <c r="B101" s="43">
+      <c r="B101" s="42">
         <v>1</v>
       </c>
-      <c r="C101" s="43">
+      <c r="C101" s="42">
         <v>3</v>
       </c>
-      <c r="D101" s="44">
+      <c r="D101" s="43">
         <v>0.94040000000000001</v>
       </c>
-      <c r="E101" s="41">
+      <c r="E101" s="40">
         <f>B101/(24-1)</f>
         <v>4.3478260869565216E-2</v>
       </c>
-      <c r="G101" s="54" t="s">
+      <c r="G101" s="52" t="s">
         <v>93</v>
       </c>
-      <c r="H101" s="16">
+      <c r="H101" s="15">
         <v>1</v>
       </c>
-      <c r="I101" s="16"/>
-      <c r="J101" s="16"/>
-      <c r="K101" s="16"/>
-      <c r="L101" s="16"/>
-      <c r="M101" s="56"/>
+      <c r="I101" s="15"/>
+      <c r="J101" s="15"/>
+      <c r="K101" s="15"/>
+      <c r="L101" s="15"/>
+      <c r="M101" s="54"/>
     </row>
     <row r="102" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A102" s="47" t="s">
+      <c r="A102" s="46" t="s">
         <v>23</v>
       </c>
-      <c r="B102" s="43">
+      <c r="B102" s="42">
         <v>3</v>
       </c>
-      <c r="C102" s="43">
+      <c r="C102" s="42">
         <v>5</v>
       </c>
-      <c r="D102" s="44">
+      <c r="D102" s="43">
         <v>0.99319999999999997</v>
       </c>
-      <c r="E102" s="49">
+      <c r="E102" s="48">
         <f>B102/(16-1)</f>
         <v>0.2</v>
       </c>
     </row>
     <row r="103" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A103" s="47" t="s">
+      <c r="A103" s="46" t="s">
         <v>23</v>
       </c>
-      <c r="B103" s="43">
+      <c r="B103" s="42">
         <v>1</v>
       </c>
-      <c r="C103" s="43">
+      <c r="C103" s="42">
         <v>4</v>
       </c>
-      <c r="D103" s="44">
+      <c r="D103" s="43">
         <v>0.97040000000000004</v>
       </c>
-      <c r="E103" s="49">
+      <c r="E103" s="48">
         <f>B103/(16-1)</f>
         <v>6.6666666666666666E-2</v>
       </c>
     </row>
     <row r="104" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A104" s="47" t="s">
+      <c r="A104" s="46" t="s">
         <v>23</v>
       </c>
-      <c r="B104" s="43">
+      <c r="B104" s="42">
         <v>0</v>
       </c>
-      <c r="C104" s="43">
+      <c r="C104" s="42">
         <v>3</v>
       </c>
-      <c r="D104" s="44">
+      <c r="D104" s="43">
         <v>0.96560000000000001</v>
       </c>
-      <c r="E104" s="49">
+      <c r="E104" s="48">
         <f>B104/(16-1)</f>
         <v>0</v>
       </c>
     </row>
     <row r="105" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A105" s="47" t="s">
+      <c r="A105" s="46" t="s">
         <v>25</v>
       </c>
-      <c r="B105" s="43">
+      <c r="B105" s="42">
         <v>1</v>
       </c>
-      <c r="C105" s="43">
+      <c r="C105" s="42">
         <v>12</v>
       </c>
-      <c r="D105" s="44">
+      <c r="D105" s="43">
         <v>0.9909</v>
       </c>
-      <c r="E105" s="41">
-        <f>B105/(32-1)</f>
+      <c r="E105" s="40">
+        <f t="shared" ref="E105:E121" si="19">B105/(32-1)</f>
         <v>3.2258064516129031E-2</v>
       </c>
     </row>
     <row r="106" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A106" s="47" t="s">
+      <c r="A106" s="46" t="s">
         <v>25</v>
       </c>
-      <c r="B106" s="43">
+      <c r="B106" s="42">
         <v>1</v>
       </c>
-      <c r="C106" s="43">
+      <c r="C106" s="42">
         <v>29</v>
       </c>
-      <c r="D106" s="44">
+      <c r="D106" s="43">
         <v>0.98399999999999999</v>
       </c>
-      <c r="E106" s="41">
-        <f>B106/(32-1)</f>
+      <c r="E106" s="40">
+        <f t="shared" si="19"/>
         <v>3.2258064516129031E-2</v>
       </c>
     </row>
     <row r="107" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A107" s="47" t="s">
+      <c r="A107" s="46" t="s">
         <v>25</v>
       </c>
-      <c r="B107" s="43">
+      <c r="B107" s="42">
         <v>1</v>
       </c>
-      <c r="C107" s="43">
+      <c r="C107" s="42">
         <v>6</v>
       </c>
-      <c r="D107" s="44">
+      <c r="D107" s="43">
         <v>0.98150000000000004</v>
       </c>
-      <c r="E107" s="41">
-        <f>B107/(32-1)</f>
+      <c r="E107" s="40">
+        <f t="shared" si="19"/>
         <v>3.2258064516129031E-2</v>
       </c>
     </row>
     <row r="108" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A108" s="47" t="s">
+      <c r="A108" s="46" t="s">
         <v>25</v>
       </c>
-      <c r="B108" s="43">
+      <c r="B108" s="42">
         <v>0</v>
       </c>
-      <c r="C108" s="43">
+      <c r="C108" s="42">
         <v>21</v>
       </c>
-      <c r="D108" s="44">
+      <c r="D108" s="43">
         <v>0.97260000000000002</v>
       </c>
-      <c r="E108" s="41">
-        <f>B108/(32-1)</f>
+      <c r="E108" s="40">
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
     <row r="109" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A109" s="47" t="s">
+      <c r="A109" s="46" t="s">
         <v>25</v>
       </c>
-      <c r="B109" s="43">
+      <c r="B109" s="42">
         <v>1</v>
       </c>
-      <c r="C109" s="43">
+      <c r="C109" s="42">
         <v>17</v>
       </c>
-      <c r="D109" s="44">
+      <c r="D109" s="43">
         <v>0.97189999999999999</v>
       </c>
-      <c r="E109" s="41">
-        <f>B109/(32-1)</f>
+      <c r="E109" s="40">
+        <f t="shared" si="19"/>
         <v>3.2258064516129031E-2</v>
       </c>
     </row>
     <row r="110" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A110" s="47" t="s">
+      <c r="A110" s="46" t="s">
         <v>25</v>
       </c>
-      <c r="B110" s="43">
+      <c r="B110" s="42">
         <v>1</v>
       </c>
-      <c r="C110" s="43">
+      <c r="C110" s="42">
         <v>25</v>
       </c>
-      <c r="D110" s="44">
+      <c r="D110" s="43">
         <v>0.94830000000000003</v>
       </c>
-      <c r="E110" s="41">
-        <f>B110/(32-1)</f>
+      <c r="E110" s="40">
+        <f t="shared" si="19"/>
         <v>3.2258064516129031E-2</v>
       </c>
     </row>
     <row r="111" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A111" s="47" t="s">
+      <c r="A111" s="46" t="s">
         <v>25</v>
       </c>
-      <c r="B111" s="43">
+      <c r="B111" s="42">
         <v>1</v>
       </c>
-      <c r="C111" s="43">
+      <c r="C111" s="42">
         <v>11</v>
       </c>
-      <c r="D111" s="44">
+      <c r="D111" s="43">
         <v>0.92679999999999996</v>
       </c>
-      <c r="E111" s="41">
-        <f>B111/(32-1)</f>
+      <c r="E111" s="40">
+        <f t="shared" si="19"/>
         <v>3.2258064516129031E-2</v>
       </c>
     </row>
     <row r="112" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A112" s="47" t="s">
+      <c r="A112" s="46" t="s">
         <v>25</v>
       </c>
-      <c r="B112" s="43">
+      <c r="B112" s="42">
         <v>1</v>
       </c>
-      <c r="C112" s="43">
+      <c r="C112" s="42">
         <v>22</v>
       </c>
-      <c r="D112" s="44">
+      <c r="D112" s="43">
         <v>0.90580000000000005</v>
       </c>
-      <c r="E112" s="41">
-        <f>B112/(32-1)</f>
+      <c r="E112" s="40">
+        <f t="shared" si="19"/>
         <v>3.2258064516129031E-2</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A113" s="47" t="s">
+      <c r="A113" s="46" t="s">
         <v>25</v>
       </c>
-      <c r="B113" s="43">
+      <c r="B113" s="42">
         <v>29</v>
       </c>
-      <c r="C113" s="43">
+      <c r="C113" s="42">
         <v>7</v>
       </c>
-      <c r="D113" s="44">
+      <c r="D113" s="43">
         <v>0.90190000000000003</v>
       </c>
-      <c r="E113" s="41">
-        <f>B113/(32-1)</f>
+      <c r="E113" s="40">
+        <f t="shared" si="19"/>
         <v>0.93548387096774188</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A114" s="47" t="s">
+      <c r="A114" s="46" t="s">
         <v>27</v>
       </c>
-      <c r="B114" s="43">
+      <c r="B114" s="42">
         <v>2</v>
       </c>
-      <c r="C114" s="43">
+      <c r="C114" s="42">
         <v>18</v>
       </c>
-      <c r="D114" s="44">
+      <c r="D114" s="43">
         <v>0.98599999999999999</v>
       </c>
-      <c r="E114" s="49">
-        <f>B114/(32-1)</f>
+      <c r="E114" s="48">
+        <f t="shared" si="19"/>
         <v>6.4516129032258063E-2</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A115" s="47" t="s">
+      <c r="A115" s="46" t="s">
         <v>27</v>
       </c>
-      <c r="B115" s="43">
+      <c r="B115" s="42">
         <v>2</v>
       </c>
-      <c r="C115" s="43">
+      <c r="C115" s="42">
         <v>8</v>
       </c>
-      <c r="D115" s="44">
+      <c r="D115" s="43">
         <v>0.96930000000000005</v>
       </c>
-      <c r="E115" s="49">
-        <f>B115/(32-1)</f>
+      <c r="E115" s="48">
+        <f t="shared" si="19"/>
         <v>6.4516129032258063E-2</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A116" s="47" t="s">
+      <c r="A116" s="46" t="s">
         <v>27</v>
       </c>
-      <c r="B116" s="43">
+      <c r="B116" s="42">
         <v>2</v>
       </c>
-      <c r="C116" s="43">
+      <c r="C116" s="42">
         <v>10</v>
       </c>
-      <c r="D116" s="44">
+      <c r="D116" s="43">
         <v>0.96930000000000005</v>
       </c>
-      <c r="E116" s="49">
-        <f>B116/(32-1)</f>
+      <c r="E116" s="48">
+        <f t="shared" si="19"/>
         <v>6.4516129032258063E-2</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A117" s="47" t="s">
+      <c r="A117" s="46" t="s">
         <v>27</v>
       </c>
-      <c r="B117" s="43">
+      <c r="B117" s="42">
         <v>1</v>
       </c>
-      <c r="C117" s="43">
+      <c r="C117" s="42">
         <v>6</v>
       </c>
-      <c r="D117" s="44">
+      <c r="D117" s="43">
         <v>0.96009999999999995</v>
       </c>
-      <c r="E117" s="49">
-        <f>B117/(32-1)</f>
+      <c r="E117" s="48">
+        <f t="shared" si="19"/>
         <v>3.2258064516129031E-2</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A118" s="47" t="s">
+      <c r="A118" s="46" t="s">
         <v>27</v>
       </c>
-      <c r="B118" s="43">
+      <c r="B118" s="42">
         <v>3</v>
       </c>
-      <c r="C118" s="43">
+      <c r="C118" s="42">
         <v>14</v>
       </c>
-      <c r="D118" s="44">
+      <c r="D118" s="43">
         <v>0.94089999999999996</v>
       </c>
-      <c r="E118" s="49">
-        <f>B118/(32-1)</f>
+      <c r="E118" s="48">
+        <f t="shared" si="19"/>
         <v>9.6774193548387094E-2</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A119" s="47" t="s">
+      <c r="A119" s="46" t="s">
         <v>27</v>
       </c>
-      <c r="B119" s="43">
+      <c r="B119" s="42">
         <v>3</v>
       </c>
-      <c r="C119" s="43">
+      <c r="C119" s="42">
         <v>23</v>
       </c>
-      <c r="D119" s="44">
+      <c r="D119" s="43">
         <v>0.93689999999999996</v>
       </c>
-      <c r="E119" s="49">
-        <f>B119/(32-1)</f>
+      <c r="E119" s="48">
+        <f t="shared" si="19"/>
         <v>9.6774193548387094E-2</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A120" s="47" t="s">
+      <c r="A120" s="46" t="s">
         <v>27</v>
       </c>
-      <c r="B120" s="43">
+      <c r="B120" s="42">
         <v>1</v>
       </c>
-      <c r="C120" s="43">
+      <c r="C120" s="42">
         <v>20</v>
       </c>
-      <c r="D120" s="44">
+      <c r="D120" s="43">
         <v>0.91259999999999997</v>
       </c>
-      <c r="E120" s="49">
-        <f>B120/(32-1)</f>
+      <c r="E120" s="48">
+        <f t="shared" si="19"/>
         <v>3.2258064516129031E-2</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A121" s="47" t="s">
+      <c r="A121" s="46" t="s">
         <v>27</v>
       </c>
-      <c r="B121" s="43">
+      <c r="B121" s="42">
         <v>1</v>
       </c>
-      <c r="C121" s="43">
+      <c r="C121" s="42">
         <v>8</v>
       </c>
-      <c r="D121" s="44">
+      <c r="D121" s="43">
         <v>0.90639999999999998</v>
       </c>
-      <c r="E121" s="49">
-        <f>B121/(32-1)</f>
+      <c r="E121" s="48">
+        <f t="shared" si="19"/>
         <v>3.2258064516129031E-2</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A122" s="47" t="s">
+      <c r="A122" s="46" t="s">
         <v>29</v>
       </c>
-      <c r="B122" s="43">
+      <c r="B122" s="42">
         <v>1</v>
       </c>
-      <c r="C122" s="43">
+      <c r="C122" s="42">
         <v>15</v>
       </c>
-      <c r="D122" s="44">
+      <c r="D122" s="43">
         <v>0.99050000000000005</v>
       </c>
-      <c r="E122" s="49">
-        <f>B122/(36-1)</f>
+      <c r="E122" s="48">
+        <f t="shared" ref="E122:E128" si="20">B122/(36-1)</f>
         <v>2.8571428571428571E-2</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A123" s="47" t="s">
+      <c r="A123" s="46" t="s">
         <v>29</v>
       </c>
-      <c r="B123" s="43">
+      <c r="B123" s="42">
         <v>1</v>
       </c>
-      <c r="C123" s="43">
+      <c r="C123" s="42">
         <v>26</v>
       </c>
-      <c r="D123" s="44">
+      <c r="D123" s="43">
         <v>0.96799999999999997</v>
       </c>
-      <c r="E123" s="49">
-        <f>B123/(36-1)</f>
+      <c r="E123" s="48">
+        <f t="shared" si="20"/>
         <v>2.8571428571428571E-2</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A124" s="47" t="s">
+      <c r="A124" s="46" t="s">
         <v>29</v>
       </c>
-      <c r="B124" s="43">
+      <c r="B124" s="42">
         <v>2</v>
       </c>
-      <c r="C124" s="43">
+      <c r="C124" s="42">
         <v>22</v>
       </c>
-      <c r="D124" s="44">
+      <c r="D124" s="43">
         <v>0.96750000000000003</v>
       </c>
-      <c r="E124" s="41">
-        <f>B124/(36-1)</f>
+      <c r="E124" s="40">
+        <f t="shared" si="20"/>
         <v>5.7142857142857141E-2</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A125" s="47" t="s">
+      <c r="A125" s="46" t="s">
         <v>29</v>
       </c>
-      <c r="B125" s="43">
+      <c r="B125" s="42">
         <v>2</v>
       </c>
-      <c r="C125" s="43">
+      <c r="C125" s="42">
         <v>32</v>
       </c>
-      <c r="D125" s="44">
+      <c r="D125" s="43">
         <v>0.9486</v>
       </c>
-      <c r="E125" s="41">
-        <f>B125/(36-1)</f>
+      <c r="E125" s="40">
+        <f t="shared" si="20"/>
         <v>5.7142857142857141E-2</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A126" s="47" t="s">
+      <c r="A126" s="46" t="s">
         <v>29</v>
       </c>
-      <c r="B126" s="43">
+      <c r="B126" s="42">
         <v>3</v>
       </c>
-      <c r="C126" s="43">
+      <c r="C126" s="42">
         <v>30</v>
       </c>
-      <c r="D126" s="44">
+      <c r="D126" s="43">
         <v>0.90910000000000002</v>
       </c>
-      <c r="E126" s="49">
-        <f>B126/(36-1)</f>
+      <c r="E126" s="48">
+        <f t="shared" si="20"/>
         <v>8.5714285714285715E-2</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A127" s="47" t="s">
+      <c r="A127" s="46" t="s">
         <v>29</v>
       </c>
-      <c r="B127" s="43">
+      <c r="B127" s="42">
         <v>3</v>
       </c>
-      <c r="C127" s="43">
+      <c r="C127" s="42">
         <v>7</v>
       </c>
-      <c r="D127" s="44">
+      <c r="D127" s="43">
         <v>0.90790000000000004</v>
       </c>
-      <c r="E127" s="49">
-        <f>B127/(36-1)</f>
+      <c r="E127" s="48">
+        <f t="shared" si="20"/>
         <v>8.5714285714285715E-2</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A128" s="48" t="s">
+      <c r="A128" s="47" t="s">
         <v>29</v>
       </c>
-      <c r="B128" s="45">
+      <c r="B128" s="44">
         <v>2</v>
       </c>
-      <c r="C128" s="45">
+      <c r="C128" s="44">
         <v>7</v>
       </c>
-      <c r="D128" s="46">
+      <c r="D128" s="45">
         <v>0.90780000000000005</v>
       </c>
-      <c r="E128" s="50">
-        <f>B128/(36-1)</f>
+      <c r="E128" s="49">
+        <f t="shared" si="20"/>
         <v>5.7142857142857141E-2</v>
       </c>
     </row>
@@ -23092,861 +23088,861 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="19" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A2" s="59" t="s">
+      <c r="A2" s="57" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="5" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A5" s="52" t="s">
+      <c r="A5" s="50" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="20" t="s">
+      <c r="B5" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="20" t="s">
+      <c r="C5" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="20" t="s">
+      <c r="D5" s="19" t="s">
         <v>103</v>
       </c>
-      <c r="E5" s="20" t="s">
+      <c r="E5" s="19" t="s">
         <v>104</v>
       </c>
-      <c r="F5" s="71" t="s">
+      <c r="F5" s="69" t="s">
         <v>105</v>
       </c>
-      <c r="G5" s="71" t="s">
+      <c r="G5" s="69" t="s">
         <v>106</v>
       </c>
-      <c r="H5" s="20" t="s">
+      <c r="H5" s="19" t="s">
         <v>107</v>
       </c>
-      <c r="I5" s="20" t="s">
+      <c r="I5" s="19" t="s">
         <v>108</v>
       </c>
-      <c r="J5" s="20" t="s">
+      <c r="J5" s="19" t="s">
         <v>109</v>
       </c>
-      <c r="K5" s="20" t="s">
+      <c r="K5" s="19" t="s">
         <v>110</v>
       </c>
-      <c r="L5" s="55" t="s">
+      <c r="L5" s="53" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A6" s="22" t="s">
+      <c r="A6" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="10">
+      <c r="B6" s="9">
         <v>12</v>
       </c>
-      <c r="C6" s="10">
+      <c r="C6" s="9">
         <v>12</v>
       </c>
-      <c r="D6" s="10">
+      <c r="D6" s="9">
         <v>46</v>
       </c>
-      <c r="E6" s="10">
+      <c r="E6" s="9">
         <v>10</v>
       </c>
-      <c r="F6" s="43">
+      <c r="F6" s="42">
         <v>10</v>
       </c>
-      <c r="G6" s="61" t="str">
+      <c r="G6" s="59" t="str">
         <f>IF(E6=F6,"✓","Δ="&amp;(E6-F6))</f>
         <v>✓</v>
       </c>
-      <c r="H6" s="10">
+      <c r="H6" s="9">
         <v>7</v>
       </c>
-      <c r="I6" s="10" t="s">
+      <c r="I6" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="J6" s="62">
+      <c r="J6" s="60">
         <f>11/(B6-1)</f>
         <v>1</v>
       </c>
-      <c r="K6" s="63">
+      <c r="K6" s="61">
         <v>1</v>
       </c>
-      <c r="L6" s="73" t="s">
+      <c r="L6" s="71" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A7" s="23" t="s">
+      <c r="A7" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="13">
+      <c r="B7" s="12">
         <v>24</v>
       </c>
-      <c r="C7" s="13">
+      <c r="C7" s="12">
         <v>16</v>
       </c>
-      <c r="D7" s="13">
+      <c r="D7" s="12">
         <v>71</v>
       </c>
-      <c r="E7" s="13">
+      <c r="E7" s="12">
         <v>22</v>
       </c>
-      <c r="F7" s="43">
+      <c r="F7" s="42">
         <v>22</v>
       </c>
-      <c r="G7" s="61" t="str">
+      <c r="G7" s="59" t="str">
         <f>IF(E7=F7,"✓","Δ="&amp;(E7-F7))</f>
         <v>✓</v>
       </c>
-      <c r="H7" s="13">
+      <c r="H7" s="12">
         <v>16</v>
       </c>
-      <c r="I7" s="13" t="s">
+      <c r="I7" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="J7" s="64">
+      <c r="J7" s="62">
         <f>9/(B7-1)</f>
         <v>0.39130434782608697</v>
       </c>
-      <c r="K7" s="65">
+      <c r="K7" s="63">
         <v>0.9758</v>
       </c>
-      <c r="L7" s="74" t="s">
+      <c r="L7" s="72" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A8" s="22" t="s">
+      <c r="A8" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="10">
+      <c r="B8" s="9">
         <v>16</v>
       </c>
-      <c r="C8" s="10">
+      <c r="C8" s="9">
         <v>8</v>
       </c>
-      <c r="D8" s="10">
+      <c r="D8" s="9">
         <v>28</v>
       </c>
-      <c r="E8" s="10">
+      <c r="E8" s="9">
         <v>11</v>
       </c>
-      <c r="F8" s="43">
+      <c r="F8" s="42">
         <v>11</v>
       </c>
-      <c r="G8" s="61" t="str">
+      <c r="G8" s="59" t="str">
         <f>IF(E8=F8,"✓","Δ="&amp;(E8-F8))</f>
         <v>✓</v>
       </c>
-      <c r="H8" s="10">
+      <c r="H8" s="9">
         <v>10</v>
       </c>
-      <c r="I8" s="10" t="s">
+      <c r="I8" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="J8" s="62">
+      <c r="J8" s="60">
         <f>6/(B8-1)</f>
         <v>0.4</v>
       </c>
-      <c r="K8" s="63">
+      <c r="K8" s="61">
         <v>0.99319999999999997</v>
       </c>
-      <c r="L8" s="73" t="s">
+      <c r="L8" s="71" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A9" s="23" t="s">
+      <c r="A9" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="13">
+      <c r="B9" s="12">
         <v>32</v>
       </c>
-      <c r="C9" s="13">
+      <c r="C9" s="12">
         <v>32</v>
       </c>
-      <c r="D9" s="13">
+      <c r="D9" s="12">
         <v>101</v>
       </c>
-      <c r="E9" s="13">
+      <c r="E9" s="12">
         <v>25</v>
       </c>
-      <c r="F9" s="43">
+      <c r="F9" s="42">
         <v>25</v>
       </c>
-      <c r="G9" s="61" t="str">
+      <c r="G9" s="59" t="str">
         <f>IF(E9=F9,"✓","Δ="&amp;(E9-F9))</f>
         <v>✓</v>
       </c>
-      <c r="H9" s="13">
+      <c r="H9" s="12">
         <v>20</v>
       </c>
-      <c r="I9" s="13" t="s">
+      <c r="I9" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="J9" s="64">
+      <c r="J9" s="62">
         <f>29/(B9-1)</f>
         <v>0.93548387096774188</v>
       </c>
-      <c r="K9" s="65">
+      <c r="K9" s="63">
         <v>0.9909</v>
       </c>
-      <c r="L9" s="74" t="s">
+      <c r="L9" s="72" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A10" s="22" t="s">
+      <c r="A10" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="10">
+      <c r="B10" s="9">
         <v>32</v>
       </c>
-      <c r="C10" s="10">
+      <c r="C10" s="9">
         <v>32</v>
       </c>
-      <c r="D10" s="10">
+      <c r="D10" s="9">
         <v>123</v>
       </c>
-      <c r="E10" s="10">
+      <c r="E10" s="9">
         <v>37</v>
       </c>
-      <c r="F10" s="43">
+      <c r="F10" s="42">
         <v>37</v>
       </c>
-      <c r="G10" s="61" t="str">
+      <c r="G10" s="59" t="str">
         <f>IF(E10=F10,"✓","Δ="&amp;(E10-F10))</f>
         <v>✓</v>
       </c>
-      <c r="H10" s="10">
+      <c r="H10" s="9">
         <v>28</v>
       </c>
-      <c r="I10" s="10" t="s">
+      <c r="I10" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="J10" s="62">
+      <c r="J10" s="60">
         <f>30/(B10-1)</f>
         <v>0.967741935483871</v>
       </c>
-      <c r="K10" s="63">
+      <c r="K10" s="61">
         <v>0.98599999999999999</v>
       </c>
-      <c r="L10" s="73" t="s">
+      <c r="L10" s="71" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A11" s="72" t="s">
+      <c r="A11" s="70" t="s">
         <v>28</v>
       </c>
-      <c r="B11" s="66">
+      <c r="B11" s="64">
         <v>36</v>
       </c>
-      <c r="C11" s="66">
+      <c r="C11" s="64">
         <v>40</v>
       </c>
-      <c r="D11" s="66">
+      <c r="D11" s="64">
         <v>119</v>
       </c>
-      <c r="E11" s="66">
+      <c r="E11" s="64">
         <v>36</v>
       </c>
-      <c r="F11" s="67" t="s">
+      <c r="F11" s="65" t="s">
         <v>118</v>
       </c>
-      <c r="G11" s="68" t="s">
+      <c r="G11" s="66" t="s">
         <v>119</v>
       </c>
-      <c r="H11" s="66">
+      <c r="H11" s="64">
         <v>24</v>
       </c>
-      <c r="I11" s="66" t="s">
+      <c r="I11" s="64" t="s">
         <v>120</v>
       </c>
-      <c r="J11" s="69">
+      <c r="J11" s="67">
         <f>34/(B11-1)</f>
         <v>0.97142857142857142</v>
       </c>
-      <c r="K11" s="70">
+      <c r="K11" s="68">
         <v>0.99050000000000005</v>
       </c>
-      <c r="L11" s="75" t="s">
+      <c r="L11" s="73" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="5" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="34" x14ac:dyDescent="0.2">
-      <c r="A14" s="115" t="s">
+      <c r="A14" s="113" t="s">
         <v>8</v>
       </c>
-      <c r="B14" s="97" t="s">
+      <c r="B14" s="95" t="s">
         <v>109</v>
       </c>
-      <c r="C14" s="97" t="s">
+      <c r="C14" s="95" t="s">
         <v>123</v>
       </c>
-      <c r="D14" s="97" t="s">
+      <c r="D14" s="95" t="s">
         <v>124</v>
       </c>
-      <c r="E14" s="97" t="s">
+      <c r="E14" s="95" t="s">
         <v>125</v>
       </c>
-      <c r="F14" s="98" t="s">
+      <c r="F14" s="96" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="34" x14ac:dyDescent="0.2">
-      <c r="A15" s="116" t="s">
+      <c r="A15" s="114" t="s">
         <v>19</v>
       </c>
-      <c r="B15" s="117">
-        <f>J6</f>
+      <c r="B15" s="115">
+        <f t="shared" ref="B15:B20" si="0">J6</f>
         <v>1</v>
       </c>
-      <c r="C15" s="118" t="s">
+      <c r="C15" s="116" t="s">
         <v>127</v>
       </c>
-      <c r="D15" s="118" t="s">
+      <c r="D15" s="116" t="s">
         <v>128</v>
       </c>
-      <c r="E15" s="119" t="s">
+      <c r="E15" s="117" t="s">
         <v>129</v>
       </c>
-      <c r="F15" s="120" t="s">
+      <c r="F15" s="118" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="34" x14ac:dyDescent="0.2">
-      <c r="A16" s="116" t="s">
+      <c r="A16" s="114" t="s">
         <v>21</v>
       </c>
-      <c r="B16" s="117">
-        <f>J7</f>
+      <c r="B16" s="115">
+        <f t="shared" si="0"/>
         <v>0.39130434782608697</v>
       </c>
-      <c r="C16" s="118" t="s">
+      <c r="C16" s="116" t="s">
         <v>127</v>
       </c>
-      <c r="D16" s="118" t="s">
+      <c r="D16" s="116" t="s">
         <v>128</v>
       </c>
-      <c r="E16" s="118" t="s">
+      <c r="E16" s="116" t="s">
         <v>131</v>
       </c>
-      <c r="F16" s="121" t="s">
+      <c r="F16" s="119" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A17" s="122" t="s">
+      <c r="A17" s="120" t="s">
         <v>23</v>
       </c>
-      <c r="B17" s="123">
-        <f>J8</f>
+      <c r="B17" s="121">
+        <f t="shared" si="0"/>
         <v>0.4</v>
       </c>
-      <c r="C17" s="124" t="s">
+      <c r="C17" s="122" t="s">
         <v>133</v>
       </c>
-      <c r="D17" s="125" t="s">
+      <c r="D17" s="123" t="s">
         <v>134</v>
       </c>
-      <c r="E17" s="126" t="s">
+      <c r="E17" s="124" t="s">
         <v>135</v>
       </c>
-      <c r="F17" s="127" t="s">
+      <c r="F17" s="125" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="A18" s="128" t="s">
+      <c r="A18" s="126" t="s">
         <v>25</v>
       </c>
-      <c r="B18" s="129">
-        <f>J9</f>
+      <c r="B18" s="127">
+        <f t="shared" si="0"/>
         <v>0.93548387096774188</v>
       </c>
-      <c r="C18" s="130" t="s">
+      <c r="C18" s="128" t="s">
         <v>137</v>
       </c>
-      <c r="D18" s="130" t="s">
+      <c r="D18" s="128" t="s">
         <v>138</v>
       </c>
-      <c r="E18" s="130" t="s">
+      <c r="E18" s="128" t="s">
         <v>139</v>
       </c>
-      <c r="F18" s="131" t="s">
+      <c r="F18" s="129" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="A19" s="128" t="s">
+      <c r="A19" s="126" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="129">
-        <f>J10</f>
+      <c r="B19" s="127">
+        <f t="shared" si="0"/>
         <v>0.967741935483871</v>
       </c>
-      <c r="C19" s="132" t="s">
+      <c r="C19" s="130" t="s">
         <v>141</v>
       </c>
-      <c r="D19" s="130" t="s">
+      <c r="D19" s="128" t="s">
         <v>142</v>
       </c>
-      <c r="E19" s="130" t="s">
+      <c r="E19" s="128" t="s">
         <v>143</v>
       </c>
-      <c r="F19" s="133" t="s">
+      <c r="F19" s="131" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A20" s="134" t="s">
+      <c r="A20" s="132" t="s">
         <v>29</v>
       </c>
-      <c r="B20" s="135">
-        <f>J11</f>
+      <c r="B20" s="133">
+        <f t="shared" si="0"/>
         <v>0.97142857142857142</v>
       </c>
-      <c r="C20" s="136" t="s">
+      <c r="C20" s="134" t="s">
         <v>145</v>
       </c>
-      <c r="D20" s="136" t="s">
+      <c r="D20" s="134" t="s">
         <v>145</v>
       </c>
-      <c r="E20" s="137" t="s">
+      <c r="E20" s="135" t="s">
         <v>146</v>
       </c>
-      <c r="F20" s="114" t="s">
+      <c r="F20" s="112" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A22" s="6" t="s">
+      <c r="A22" s="5" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A23" s="52" t="s">
+      <c r="A23" s="50" t="s">
         <v>8</v>
       </c>
-      <c r="B23" s="20" t="s">
+      <c r="B23" s="19" t="s">
         <v>109</v>
       </c>
-      <c r="C23" s="20" t="s">
+      <c r="C23" s="19" t="s">
         <v>149</v>
       </c>
-      <c r="D23" s="55" t="s">
+      <c r="D23" s="53" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A24" s="78" t="s">
+      <c r="A24" s="76" t="s">
         <v>19</v>
       </c>
-      <c r="B24" s="64">
-        <f>J6</f>
+      <c r="B24" s="62">
+        <f t="shared" ref="B24:B29" si="1">J6</f>
         <v>1</v>
       </c>
-      <c r="C24" s="13">
-        <f>E6</f>
+      <c r="C24" s="12">
+        <f t="shared" ref="C24:C29" si="2">E6</f>
         <v>10</v>
       </c>
-      <c r="D24" s="28">
+      <c r="D24" s="27">
         <v>11</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A25" s="78" t="s">
+      <c r="A25" s="76" t="s">
         <v>21</v>
       </c>
-      <c r="B25" s="64">
-        <f>J7</f>
+      <c r="B25" s="62">
+        <f t="shared" si="1"/>
         <v>0.39130434782608697</v>
       </c>
-      <c r="C25" s="13">
-        <f>E7</f>
+      <c r="C25" s="12">
+        <f t="shared" si="2"/>
         <v>22</v>
       </c>
-      <c r="D25" s="28">
+      <c r="D25" s="27">
         <v>9</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A26" s="78" t="s">
+      <c r="A26" s="76" t="s">
         <v>23</v>
       </c>
-      <c r="B26" s="64">
-        <f>J8</f>
+      <c r="B26" s="62">
+        <f t="shared" si="1"/>
         <v>0.4</v>
       </c>
-      <c r="C26" s="13">
-        <f>E8</f>
+      <c r="C26" s="12">
+        <f t="shared" si="2"/>
         <v>11</v>
       </c>
-      <c r="D26" s="28">
+      <c r="D26" s="27">
         <v>6</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A27" s="78" t="s">
+      <c r="A27" s="76" t="s">
         <v>25</v>
       </c>
-      <c r="B27" s="64">
-        <f>J9</f>
+      <c r="B27" s="62">
+        <f t="shared" si="1"/>
         <v>0.93548387096774188</v>
       </c>
-      <c r="C27" s="13">
-        <f>E9</f>
+      <c r="C27" s="12">
+        <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="D27" s="28">
+      <c r="D27" s="27">
         <v>29</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A28" s="78" t="s">
+      <c r="A28" s="76" t="s">
         <v>27</v>
       </c>
-      <c r="B28" s="64">
-        <f>J10</f>
+      <c r="B28" s="62">
+        <f t="shared" si="1"/>
         <v>0.967741935483871</v>
       </c>
-      <c r="C28" s="13">
-        <f>E10</f>
+      <c r="C28" s="12">
+        <f t="shared" si="2"/>
         <v>37</v>
       </c>
-      <c r="D28" s="28">
+      <c r="D28" s="27">
         <v>30</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A29" s="79" t="s">
+      <c r="A29" s="77" t="s">
         <v>29</v>
       </c>
-      <c r="B29" s="76">
-        <f>J11</f>
+      <c r="B29" s="74">
+        <f t="shared" si="1"/>
         <v>0.97142857142857142</v>
       </c>
-      <c r="C29" s="77">
-        <f>E11</f>
+      <c r="C29" s="75">
+        <f t="shared" si="2"/>
         <v>36</v>
       </c>
-      <c r="D29" s="80">
+      <c r="D29" s="78">
         <v>34</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A31" s="6" t="s">
+      <c r="A31" s="5" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A32" s="60" t="s">
+      <c r="A32" s="58" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A34" s="52" t="s">
+      <c r="A34" s="50" t="s">
         <v>82</v>
       </c>
-      <c r="B34" s="20" t="s">
+      <c r="B34" s="19" t="s">
         <v>152</v>
       </c>
-      <c r="C34" s="20" t="s">
+      <c r="C34" s="19" t="s">
         <v>84</v>
       </c>
-      <c r="D34" s="20" t="s">
+      <c r="D34" s="19" t="s">
         <v>153</v>
       </c>
-      <c r="E34" s="55" t="s">
+      <c r="E34" s="53" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A35" s="88">
+      <c r="A35" s="86">
         <v>0</v>
       </c>
-      <c r="B35" s="81" t="s">
+      <c r="B35" s="79" t="s">
         <v>155</v>
       </c>
-      <c r="C35" s="81" t="s">
+      <c r="C35" s="79" t="s">
         <v>156</v>
       </c>
-      <c r="D35" s="81" t="s">
+      <c r="D35" s="79" t="s">
         <v>157</v>
       </c>
-      <c r="E35" s="92" t="s">
+      <c r="E35" s="90" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A36" s="88">
+      <c r="A36" s="86">
         <v>1</v>
       </c>
-      <c r="B36" s="81" t="s">
+      <c r="B36" s="79" t="s">
         <v>158</v>
       </c>
-      <c r="C36" s="82" t="s">
+      <c r="C36" s="80" t="s">
         <v>159</v>
       </c>
-      <c r="D36" s="81" t="s">
+      <c r="D36" s="79" t="s">
         <v>160</v>
       </c>
-      <c r="E36" s="92" t="s">
+      <c r="E36" s="90" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A37" s="88">
+      <c r="A37" s="86">
         <v>2</v>
       </c>
-      <c r="B37" s="81" t="s">
+      <c r="B37" s="79" t="s">
         <v>161</v>
       </c>
-      <c r="C37" s="82" t="s">
+      <c r="C37" s="80" t="s">
         <v>162</v>
       </c>
-      <c r="D37" s="81" t="s">
+      <c r="D37" s="79" t="s">
         <v>160</v>
       </c>
-      <c r="E37" s="92" t="s">
+      <c r="E37" s="90" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A38" s="88">
+      <c r="A38" s="86">
         <v>3</v>
       </c>
-      <c r="B38" s="81" t="s">
+      <c r="B38" s="79" t="s">
         <v>163</v>
       </c>
-      <c r="C38" s="81" t="s">
+      <c r="C38" s="79" t="s">
         <v>164</v>
       </c>
-      <c r="D38" s="81" t="s">
+      <c r="D38" s="79" t="s">
         <v>160</v>
       </c>
-      <c r="E38" s="92" t="s">
+      <c r="E38" s="90" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A39" s="89"/>
-      <c r="B39" s="83" t="s">
+      <c r="A39" s="87"/>
+      <c r="B39" s="81" t="s">
         <v>165</v>
       </c>
-      <c r="C39" s="84"/>
-      <c r="D39" s="84"/>
-      <c r="E39" s="93"/>
+      <c r="C39" s="82"/>
+      <c r="D39" s="82"/>
+      <c r="E39" s="91"/>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A40" s="88">
+      <c r="A40" s="86">
         <v>5</v>
       </c>
-      <c r="B40" s="81" t="s">
+      <c r="B40" s="79" t="s">
         <v>166</v>
       </c>
-      <c r="C40" s="65">
+      <c r="C40" s="63">
         <v>0.56759999999999999</v>
       </c>
-      <c r="D40" s="81" t="s">
+      <c r="D40" s="79" t="s">
         <v>157</v>
       </c>
-      <c r="E40" s="92" t="s">
+      <c r="E40" s="90" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A41" s="53" t="s">
+      <c r="A41" s="51" t="s">
         <v>168</v>
       </c>
-      <c r="B41" s="81" t="s">
+      <c r="B41" s="79" t="s">
         <v>169</v>
       </c>
-      <c r="C41" s="13" t="s">
+      <c r="C41" s="12" t="s">
         <v>170</v>
       </c>
-      <c r="D41" s="81" t="s">
+      <c r="D41" s="79" t="s">
         <v>157</v>
       </c>
-      <c r="E41" s="92" t="s">
+      <c r="E41" s="90" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A42" s="89"/>
-      <c r="B42" s="83" t="s">
+      <c r="A42" s="87"/>
+      <c r="B42" s="81" t="s">
         <v>172</v>
       </c>
-      <c r="C42" s="84"/>
-      <c r="D42" s="84"/>
-      <c r="E42" s="93"/>
+      <c r="C42" s="82"/>
+      <c r="D42" s="82"/>
+      <c r="E42" s="91"/>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A43" s="90">
+      <c r="A43" s="88">
         <v>30</v>
       </c>
-      <c r="B43" s="85" t="s">
+      <c r="B43" s="83" t="s">
         <v>173</v>
       </c>
-      <c r="C43" s="86">
+      <c r="C43" s="84">
         <v>0.52170000000000005</v>
       </c>
-      <c r="D43" s="85" t="s">
+      <c r="D43" s="83" t="s">
         <v>157</v>
       </c>
-      <c r="E43" s="94" t="s">
+      <c r="E43" s="92" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A44" s="90">
+      <c r="A44" s="88">
         <v>33</v>
       </c>
-      <c r="B44" s="85" t="s">
+      <c r="B44" s="83" t="s">
         <v>175</v>
       </c>
-      <c r="C44" s="87" t="s">
+      <c r="C44" s="85" t="s">
         <v>176</v>
       </c>
-      <c r="D44" s="85" t="s">
+      <c r="D44" s="83" t="s">
         <v>160</v>
       </c>
-      <c r="E44" s="94" t="s">
+      <c r="E44" s="92" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A45" s="91">
+      <c r="A45" s="89">
         <v>34</v>
       </c>
-      <c r="B45" s="66" t="s">
+      <c r="B45" s="64" t="s">
         <v>178</v>
       </c>
-      <c r="C45" s="70">
+      <c r="C45" s="68">
         <v>0.53939999999999999</v>
       </c>
-      <c r="D45" s="66" t="s">
+      <c r="D45" s="64" t="s">
         <v>157</v>
       </c>
-      <c r="E45" s="95" t="s">
+      <c r="E45" s="93" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A47" s="6" t="s">
+      <c r="A47" s="5" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="A48" s="96" t="s">
+      <c r="A48" s="94" t="s">
         <v>181</v>
       </c>
-      <c r="B48" s="97" t="s">
+      <c r="B48" s="95" t="s">
         <v>182</v>
       </c>
-      <c r="C48" s="97" t="s">
+      <c r="C48" s="95" t="s">
         <v>183</v>
       </c>
-      <c r="D48" s="98" t="s">
+      <c r="D48" s="96" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="51" x14ac:dyDescent="0.2">
-      <c r="A49" s="99" t="s">
+      <c r="A49" s="97" t="s">
         <v>185</v>
       </c>
-      <c r="B49" s="100" t="s">
+      <c r="B49" s="98" t="s">
         <v>186</v>
       </c>
-      <c r="C49" s="101" t="s">
+      <c r="C49" s="99" t="s">
         <v>187</v>
       </c>
-      <c r="D49" s="102" t="s">
+      <c r="D49" s="100" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="51" x14ac:dyDescent="0.2">
-      <c r="A50" s="103" t="s">
+      <c r="A50" s="101" t="s">
         <v>189</v>
       </c>
-      <c r="B50" s="104" t="s">
+      <c r="B50" s="102" t="s">
         <v>190</v>
       </c>
-      <c r="C50" s="101" t="s">
+      <c r="C50" s="99" t="s">
         <v>187</v>
       </c>
-      <c r="D50" s="105" t="s">
+      <c r="D50" s="103" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="68" x14ac:dyDescent="0.2">
-      <c r="A51" s="99" t="s">
+      <c r="A51" s="97" t="s">
         <v>192</v>
       </c>
-      <c r="B51" s="100" t="s">
+      <c r="B51" s="98" t="s">
         <v>193</v>
       </c>
-      <c r="C51" s="106" t="s">
+      <c r="C51" s="104" t="s">
         <v>194</v>
       </c>
-      <c r="D51" s="102" t="s">
+      <c r="D51" s="100" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="52" spans="1:4" ht="68" x14ac:dyDescent="0.2">
-      <c r="A52" s="103" t="s">
+      <c r="A52" s="101" t="s">
         <v>196</v>
       </c>
-      <c r="B52" s="104" t="s">
+      <c r="B52" s="102" t="s">
         <v>197</v>
       </c>
-      <c r="C52" s="106" t="s">
+      <c r="C52" s="104" t="s">
         <v>198</v>
       </c>
-      <c r="D52" s="105" t="s">
+      <c r="D52" s="103" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="68" x14ac:dyDescent="0.2">
-      <c r="A53" s="107" t="s">
+      <c r="A53" s="105" t="s">
         <v>200</v>
       </c>
-      <c r="B53" s="108" t="s">
+      <c r="B53" s="106" t="s">
         <v>201</v>
       </c>
-      <c r="C53" s="109" t="s">
+      <c r="C53" s="107" t="s">
         <v>202</v>
       </c>
-      <c r="D53" s="110" t="s">
+      <c r="D53" s="108" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="68" x14ac:dyDescent="0.2">
-      <c r="A54" s="111" t="s">
+      <c r="A54" s="109" t="s">
         <v>204</v>
       </c>
-      <c r="B54" s="112" t="s">
+      <c r="B54" s="110" t="s">
         <v>205</v>
       </c>
-      <c r="C54" s="113" t="s">
+      <c r="C54" s="111" t="s">
         <v>202</v>
       </c>
-      <c r="D54" s="114" t="s">
+      <c r="D54" s="112" t="s">
         <v>206</v>
       </c>
     </row>

--- a/accessibility-knowledge-emergence/results/analysis/AttentionBindingPythiaModels-ClaudeInExcel.xlsx
+++ b/accessibility-knowledge-emergence/results/analysis/AttentionBindingPythiaModels-ClaudeInExcel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trishasalas/Repos/Research/how-models-think/accessibility-knowledge-emergence/results/analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10FCDC74-43D0-E549-B254-7ABE56F5CBA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F22CFAE-9D4B-494D-A79A-71BC3266D1DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17180" xr2:uid="{81DF49B0-1BA3-D947-B774-10FF709E1CBE}"/>
+    <workbookView xWindow="38400" yWindow="600" windowWidth="38400" windowHeight="21000" activeTab="7" xr2:uid="{81DF49B0-1BA3-D947-B774-10FF709E1CBE}"/>
   </bookViews>
   <sheets>
     <sheet name="Claude Log" sheetId="12" r:id="rId1"/>
